--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -577,14 +577,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Jun 25</t>
+          <t>Ene 18</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45809</v>
+        <v>43101</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4.317429</v>
+        <v>5.545835</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -635,18 +635,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Feb 18</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45839</v>
+        <v>43132</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3.512423</v>
+        <v>5.339217</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-0.8 puntos porcentuales</t>
+          <t>-0.2 puntos porcentuales</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -693,18 +693,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ago 25</t>
+          <t>Mar 18</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45870</v>
+        <v>43160</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3.568777</v>
+        <v>5.035412</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+0.1 puntos porcentuales</t>
+          <t>-0.3 puntos porcentuales</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -751,18 +751,18 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>Abr 18</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45901</v>
+        <v>43191</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3.760288</v>
+        <v>4.550783</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>+0.2 puntos porcentuales</t>
+          <t>-0.5 puntos porcentuales</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -809,18 +809,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>May 18</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45931</v>
+        <v>43221</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3.566521</v>
+        <v>4.506269</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-0.2 puntos porcentuales</t>
+          <t>0.0 puntos porcentuales</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -867,18 +867,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Jun 18</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45962</v>
+        <v>43252</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3.799191</v>
+        <v>4.646858</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>+0.2 puntos porcentuales</t>
+          <t>+0.1 puntos porcentuales</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -925,18 +925,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Jul 18</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45992</v>
+        <v>43282</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3.691944</v>
+        <v>4.811406</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>-0.1 puntos porcentuales</t>
+          <t>+0.2 puntos porcentuales</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -983,14 +983,14 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Ene 26</t>
+          <t>Ago 18</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>46023</v>
+        <v>43313</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3.791301</v>
+        <v>4.904528</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Sep 18</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>46054</v>
+        <v>43344</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4.023038</v>
+        <v>5.019574</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>+0.2 puntos porcentuales</t>
+          <t>+0.1 puntos porcentuales</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1099,18 +1099,18 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Oct 18</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>46082</v>
+        <v>43374</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>4.586774</v>
+        <v>4.903636</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>+0.6 puntos porcentuales</t>
+          <t>-0.1 puntos porcentuales</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1157,18 +1157,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Nov 18</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>46113</v>
+        <v>43405</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>4.448503</v>
+        <v>4.716534</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-0.1 puntos porcentuales</t>
+          <t>-0.2 puntos porcentuales</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Dic 18</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>46143</v>
+        <v>43435</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>3.938948</v>
+        <v>4.830546</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>-0.5 puntos porcentuales</t>
+          <t>+0.1 puntos porcentuales</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1273,18 +1273,18 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Ene 19</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>46174</v>
+        <v>43466</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3.365977</v>
+        <v>4.365606</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>-0.6 puntos porcentuales</t>
+          <t>-0.5 puntos porcentuales</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1331,56 +1331,5218 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>Feb 19</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>43497</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>3.940276</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>-0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Mar 19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>43525</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>4.004178</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>+0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Abr 19</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>4.413453</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>+0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>May 19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>43586</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>4.281993</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>-0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Jun 19</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>43617</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>3.947147</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>-0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Jul 19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>3.781338</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Ago 19</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>43678</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>3.162441</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>-0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sep 19</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>43709</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2.997513</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Oct 19</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>3.019519</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>+0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Nov 19</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>43770</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2.974497</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Dic 19</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>43800</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>2.828577</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>-0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ene 20</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>3.238352</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>+0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Feb 20</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>43862</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>3.696194</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>+0.5 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mar 20</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>43891</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>3.249063</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>-0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Abr 20</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>2.148149</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>-1.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43952</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>2.837271</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>+0.7 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Jun 20</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>43983</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>3.334011</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>+0.5 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>3.623405</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>+0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Ago 20</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>44044</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>4.048423</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>+0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sep 20</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>44075</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>4.013777</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Oct 20</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>4.086964</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>+0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nov 20</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>44136</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>3.331878</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>-0.8 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Dic 20</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>44166</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>3.150075</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Ene 21</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>3.535093</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>+0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Feb 21</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>44228</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>3.75904</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Mar 21</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>44256</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>4.666879</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>+0.9 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Abr 21</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>6.084819</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>+1.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>44317</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>5.893823</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>44348</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>5.878606</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Jul 21</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>5.805815</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>-0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Ago 21</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>44409</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>5.592072</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sep 21</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>44440</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>6.000148</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>+0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Oct 21</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>6.239543</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Nov 21</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>44501</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>7.374881</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>+1.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Dic 21</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>44531</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>7.355108</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Ene 22</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>7.070139</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>-0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Feb 22</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>44593</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>7.279973</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>44621</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>7.453677</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Abr 22</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>7.682503</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>44682</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>7.652621</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>44713</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>7.986338</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>+0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Jul 22</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>8.150807</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Ago 22</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>44774</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>8.695423</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>+0.5 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Sep 22</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>44805</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>8.69975</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>+0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Oct 22</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>8.406815</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>-0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Nov 22</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>44866</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>7.796619</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>-0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Dic 22</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>44896</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>7.817029</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>+0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Ene 23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>7.910035</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>+0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Feb 23</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>44958</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>7.618864</v>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>-0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>44986</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>6.849258</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>-0.8 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Abr 23</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>6.252845</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>-0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>45047</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>5.835303</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>-0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>45078</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>5.055554</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>-0.8 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Jul 23</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>4.785763</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>-0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Ago 23</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>45139</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>4.638014</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>-0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Sep 23</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>45170</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>4.454488</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Oct 23</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>4.257001</v>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Nov 23</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>45231</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>4.323912</v>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>+0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Dic 23</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>4.66089</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>+0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Ene 24</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>4.883929</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Feb 24</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>45323</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>4.400762</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>-0.5 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Mar 24</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>4.420939</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>+0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Abr 24</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>4.65321</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>May 24</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>45413</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>4.686768</v>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>+0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>45444</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>4.976056</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>+0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Jul 24</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>5.566164</v>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>+0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Ago 24</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>45505</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>4.99286</v>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>-0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Sep 24</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>45536</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>4.580387</v>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>-0.4 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Oct 24</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>4.76154</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>45597</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>4.548671</v>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>45627</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>4.212339</v>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>-0.3 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Ene 25</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>3.58504</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>-0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>45689</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>3.77391</v>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>45717</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>3.801141</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>+0.0 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>3.933421</v>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>+0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>4.418773</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>+0.5 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>4.317429</v>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>-0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>3.512423</v>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>-0.8 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Ago 25</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>3.568777</v>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>+0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>3.760288</v>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>3.566521</v>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>-0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>3.799191</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Dic 25</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>3.691944</v>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>-0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Ene 26</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>3.791301</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>+0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>4.023038</v>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>+0.2 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>4.586774</v>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>+0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>4.448503</v>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>-0.1 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>3.938948</v>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>-0.5 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>3.365977</v>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>-0.6 puntos porcentuales</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>07 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B108" s="5" t="n">
         <v>46204</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C108" s="6" t="n">
         <v>3.11763</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>-0.2 puntos porcentuales</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Variación anual (%)</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>Variación anual (%)</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
         <is>
           <t>07 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452 · Fecha de publicación: 07 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf · Fecha de publicación: 07 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452 · Fecha de publicación: 07 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf · Fecha de publicación: 7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3175,12 +3175,12 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3291,12 +3291,12 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3523,12 +3523,12 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3639,12 +3639,12 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4161,12 +4161,12 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4277,12 +4277,12 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4393,12 +4393,12 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4683,12 +4683,12 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4973,12 +4973,12 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5147,12 +5147,12 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5205,12 +5205,12 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5263,12 +5263,12 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5321,12 +5321,12 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5437,12 +5437,12 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5785,12 +5785,12 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6017,12 +6017,12 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6133,12 +6133,12 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6307,12 +6307,12 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6365,12 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6481,12 +6481,12 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026</t>
+          <t>7 de agosto de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -18,7 +18,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.000&quot; p.p.&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -96,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,8 +108,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:X108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -482,10 +488,25 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación anual (%)</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 / Porcentaje</t>
         </is>
       </c>
     </row>
@@ -522,35 +543,110 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Inflación</t>
+          <t>INPC (índice)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Subyacente</t>
+          <t>INPC var. mensual (%)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>No subyacente</t>
+          <t>INPC inflación anual (%)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>Subyacente (índice)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Subyacente var. mensual (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Subyacente inflación anual (%)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Mercancías var. mensual (%)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Mercancías inflación anual (%)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Servicios var. mensual (%)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Servicios inflación anual (%)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>No subyacente var. mensual (%)</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>No subyacente inflación anual (%)</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Agropecuarios var. mensual (%)</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Agropecuarios inflación anual (%)</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Energéticos y tarifas var. mensual (%)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Energéticos y tarifas inflación anual (%)</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Incidencia subyacente (p.p.)</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Incidencia no subyacente (p.p.)</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
           <t>Carácter del dato</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>URL del boletín</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Fecha de publicación</t>
         </is>
@@ -566,28 +662,71 @@
         <v>43101</v>
       </c>
       <c r="C6" s="6" t="n">
+        <v>98.795</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.531293</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>5.545835</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="F6" s="6" t="n">
+        <v>98.252014</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.283751</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <v>4.561087</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="n">
+        <v>0.558061</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>5.777404</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0.044417</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>3.517202</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>1.238993</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>8.439624999999999</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>0.029293</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>10.76128</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>1.974143</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>7.101367</v>
+      </c>
+      <c r="S6" s="8" t="n"/>
+      <c r="T6" s="8" t="n"/>
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X6" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -602,29 +741,72 @@
       <c r="B7" s="5" t="n">
         <v>43132</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="10" t="n">
+        <v>99.171374</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.380965</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>5.339217</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="F7" s="10" t="n">
+        <v>98.73168800000001</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.488208</v>
+      </c>
+      <c r="H7" s="11" t="n">
         <v>4.274663</v>
       </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="11" t="n">
+        <v>0.536852</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>5.182968</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.445549</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>3.490211</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>0.078953</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>8.491229000000001</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>-1.895167</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>9.692080000000001</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>1.25577</v>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>7.809554</v>
+      </c>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="12" t="n"/>
+      <c r="U7" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V7" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X7" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -640,28 +822,71 @@
         <v>43160</v>
       </c>
       <c r="C8" s="6" t="n">
+        <v>99.49215700000001</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0.323463</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>5.035412</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="F8" s="6" t="n">
+        <v>99.057357</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.329853</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <v>4.022869</v>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="n">
+        <v>0.253656</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>4.637305</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.396736</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>3.490208</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.302932</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>8.027089999999999</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>0.379106</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>7.742415</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>0.258937</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>8.192394999999999</v>
+      </c>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X8" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -676,29 +901,72 @@
       <c r="B9" s="5" t="n">
         <v>43191</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="10" t="n">
+        <v>99.154847</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>-0.339032</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>4.550783</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="F9" s="10" t="n">
+        <v>99.20320599999999</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>0.147237</v>
+      </c>
+      <c r="H9" s="11" t="n">
         <v>3.709564</v>
       </c>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="11" t="n">
+        <v>0.331897</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>4.353791</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>-0.014621</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>3.14947</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>-1.720028</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>7.071345</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>-0.494502</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>5.23864</v>
+      </c>
+      <c r="Q9" s="11" t="n">
+        <v>-2.428706</v>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>8.182373999999999</v>
+      </c>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="12" t="n"/>
+      <c r="U9" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X9" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -714,28 +982,71 @@
         <v>43221</v>
       </c>
       <c r="C10" s="6" t="n">
+        <v>98.99408</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>-0.162137</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>4.506269</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="F10" s="6" t="n">
+        <v>99.458112</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.256953</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <v>3.690656</v>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="n">
+        <v>0.210207</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>4.074199</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0.298068</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>3.355929</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>-1.377538</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>6.98794</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>-1.0702</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>2.871721</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>-1.558784</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>9.586672999999999</v>
+      </c>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V10" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X10" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -750,29 +1061,72 @@
       <c r="B11" s="5" t="n">
         <v>43252</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="10" t="n">
+        <v>99.376465</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>4.646858</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="F11" s="10" t="n">
+        <v>99.688327</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>0.23147</v>
+      </c>
+      <c r="H11" s="11" t="n">
         <v>3.615292</v>
       </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="11" t="n">
+        <v>0.128801</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>3.87966</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>0.321693</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>3.384522</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>0.841551</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>7.791677</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>-0.322875</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>2.107352</v>
+      </c>
+      <c r="Q11" s="11" t="n">
+        <v>1.531653</v>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>11.399977</v>
+      </c>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="12" t="n"/>
+      <c r="U11" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V11" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X11" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -788,28 +1142,71 @@
         <v>43282</v>
       </c>
       <c r="C12" s="6" t="n">
+        <v>99.909099</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.535976</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>4.811406</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="F12" s="6" t="n">
+        <v>99.97429200000001</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.286859</v>
+      </c>
+      <c r="H12" s="7" t="n">
         <v>3.634916</v>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="n">
+        <v>0.224457</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>3.990822</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.341592</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>3.325112</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>1.266213</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>8.381461</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>1.908602</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>1.530655</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>0.892452</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>12.856737</v>
+      </c>
+      <c r="S12" s="8" t="n"/>
+      <c r="T12" s="8" t="n"/>
+      <c r="U12" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V12" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -824,29 +1221,72 @@
       <c r="B13" s="5" t="n">
         <v>43313</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="10" t="n">
+        <v>100.492</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>0.583431</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>4.904528</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="F13" s="10" t="n">
+        <v>100.220344</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>0.246115</v>
+      </c>
+      <c r="H13" s="11" t="n">
         <v>3.626895</v>
       </c>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="11" t="n">
+        <v>0.386106</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>3.901135</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>0.092714</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>3.355441</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>1.61452</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>8.802117000000001</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>1.899774</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>1.370686</v>
+      </c>
+      <c r="Q13" s="11" t="n">
+        <v>1.420054</v>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>13.693492</v>
+      </c>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="12" t="n"/>
+      <c r="U13" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V13" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X13" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -862,28 +1302,71 @@
         <v>43344</v>
       </c>
       <c r="C14" s="6" t="n">
+        <v>100.917</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.422919</v>
+      </c>
+      <c r="E14" s="7" t="n">
         <v>5.019574</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="F14" s="6" t="n">
+        <v>100.544773</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0.323716</v>
+      </c>
+      <c r="H14" s="7" t="n">
         <v>3.669772</v>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="7" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>3.953942</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>0.262106</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>3.377403</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.726812</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>9.150411999999999</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>-0.213119</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>1.217785</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>1.404114</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>14.471202</v>
+      </c>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -898,29 +1381,72 @@
       <c r="B15" s="5" t="n">
         <v>43374</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="10" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0.518248</v>
+      </c>
+      <c r="E15" s="11" t="n">
         <v>4.903636</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="F15" s="10" t="n">
+        <v>100.856606</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>0.310143</v>
+      </c>
+      <c r="H15" s="11" t="n">
         <v>3.729408</v>
       </c>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="11" t="n">
+        <v>0.239012</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>3.978287</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0.387274</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>3.483058</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>1.152934</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>8.499081</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>-0.701962</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>2.434155</v>
+      </c>
+      <c r="Q15" s="11" t="n">
+        <v>2.468231</v>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>12.619568</v>
+      </c>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="12" t="n"/>
+      <c r="U15" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X15" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -936,28 +1462,71 @@
         <v>43405</v>
       </c>
       <c r="C16" s="6" t="n">
+        <v>102.303</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0.850749</v>
+      </c>
+      <c r="E16" s="7" t="n">
         <v>4.716534</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="F16" s="6" t="n">
+        <v>101.110443</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.251681</v>
+      </c>
+      <c r="H16" s="7" t="n">
         <v>3.633672</v>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="n">
+        <v>0.263924</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>3.903935</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0.238426</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>3.366115</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>2.6564</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>8.072717000000001</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>3.478029</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>4.78025</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>2.091812</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>10.301016</v>
+      </c>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V16" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X16" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -972,29 +1541,72 @@
       <c r="B17" s="5" t="n">
         <v>43435</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="10" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0.700859</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>4.830546</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="F17" s="10" t="n">
+        <v>101.582475</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>0.466848</v>
+      </c>
+      <c r="H17" s="11" t="n">
         <v>3.683082</v>
       </c>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="11" t="n">
+        <v>0.338042</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>3.919391</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>0.6063499999999999</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>3.472665</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>1.393183</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>8.398502000000001</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>4.029437</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>7.061474</v>
+      </c>
+      <c r="Q17" s="11" t="n">
+        <v>-0.442933</v>
+      </c>
+      <c r="R17" s="11" t="n">
+        <v>9.099752000000001</v>
+      </c>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V17" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X17" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1010,28 +1622,71 @@
         <v>43466</v>
       </c>
       <c r="C18" s="6" t="n">
+        <v>103.108</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0.08542</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>4.365606</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="F18" s="6" t="n">
+        <v>101.784796</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.199169</v>
+      </c>
+      <c r="H18" s="7" t="n">
         <v>3.595633</v>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="7" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>3.659019</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>0.08365599999999999</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>3.513248</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>-0.246668</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>6.807776</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>0.351918</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>7.406779</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>-0.682303</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>6.257682</v>
+      </c>
+      <c r="S18" s="8" t="n"/>
+      <c r="T18" s="8" t="n"/>
+      <c r="U18" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V18" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X18" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1046,29 +1701,72 @@
       <c r="B19" s="5" t="n">
         <v>43497</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="10" t="n">
+        <v>103.079</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>-0.028126</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>3.940276</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="F19" s="10" t="n">
+        <v>102.224173</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>0.431673</v>
+      </c>
+      <c r="H19" s="11" t="n">
         <v>3.537349</v>
       </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="11" t="n">
+        <v>0.493346</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>3.614162</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>0.364908</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>3.430145</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>-1.377917</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>5.252954</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>-4.277942</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>4.798078</v>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>0.754625</v>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>5.731782</v>
+      </c>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="12" t="n"/>
+      <c r="U19" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V19" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X19" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1084,28 +1782,71 @@
         <v>43525</v>
       </c>
       <c r="C20" s="6" t="n">
+        <v>103.476</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.385141</v>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>4.004178</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="F20" s="6" t="n">
+        <v>102.57614</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="H20" s="7" t="n">
         <v>3.552268</v>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="7" t="n">
+        <v>0.341929</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>3.705394</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>3.378793</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.50647</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>5.466537</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>-0.670552</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>3.702212</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>1.328765</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>6.860009</v>
+      </c>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V20" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X20" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1120,29 +1861,72 @@
       <c r="B21" s="5" t="n">
         <v>43556</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="10" t="n">
+        <v>103.531</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>0.053152</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>4.413453</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="F21" s="10" t="n">
+        <v>103.043284</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>0.455412</v>
+      </c>
+      <c r="H21" s="11" t="n">
         <v>3.870921</v>
       </c>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="11" t="n">
+        <v>0.363196</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>3.737746</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>0.5553630000000001</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>3.968122</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>-1.146453</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>6.082053</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0.5270550000000001</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>4.766854</v>
+      </c>
+      <c r="Q21" s="11" t="n">
+        <v>-2.292537</v>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>7.009141</v>
+      </c>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="12" t="n"/>
+      <c r="U21" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X21" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1158,28 +1942,71 @@
         <v>43586</v>
       </c>
       <c r="C22" s="6" t="n">
+        <v>103.233</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>-0.287836</v>
+      </c>
+      <c r="E22" s="7" t="n">
         <v>4.281993</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="F22" s="6" t="n">
+        <v>103.212248</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0.163974</v>
+      </c>
+      <c r="H22" s="7" t="n">
         <v>3.774591</v>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="n">
+        <v>0.286847</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>3.817084</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>0.031048</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>3.691331</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>-1.658457</v>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>5.779886</v>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>0.169395</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>6.079587</v>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>-2.946364</v>
+      </c>
+      <c r="R22" s="7" t="n">
+        <v>5.500793</v>
+      </c>
+      <c r="S22" s="8" t="n"/>
+      <c r="T22" s="8" t="n"/>
+      <c r="U22" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V22" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X22" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1194,29 +2021,72 @@
       <c r="B23" s="5" t="n">
         <v>43617</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="10" t="n">
+        <v>103.299</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>0.063933</v>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>3.947147</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="F23" s="10" t="n">
+        <v>103.525562</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>0.303562</v>
+      </c>
+      <c r="H23" s="11" t="n">
         <v>3.849232</v>
       </c>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="11" t="n">
+        <v>0.231019</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>3.923067</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>3.753912</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>-0.67611</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>4.187903</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>-0.179378</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>6.2323</v>
+      </c>
+      <c r="Q23" s="11" t="n">
+        <v>-1.037345</v>
+      </c>
+      <c r="R23" s="11" t="n">
+        <v>2.831366</v>
+      </c>
+      <c r="S23" s="12" t="n"/>
+      <c r="T23" s="12" t="n"/>
+      <c r="U23" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V23" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X23" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1232,28 +2102,71 @@
         <v>43647</v>
       </c>
       <c r="C24" s="6" t="n">
+        <v>103.687</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.375609</v>
+      </c>
+      <c r="E24" s="7" t="n">
         <v>3.781338</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="F24" s="6" t="n">
+        <v>103.794405</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0.259688</v>
+      </c>
+      <c r="H24" s="7" t="n">
         <v>3.821096</v>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="n">
+        <v>0.150361</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>3.846237</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0.378082</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>3.791643</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.737941</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>3.64439</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>1.999333</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>6.32688</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>-0.187323</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>1.730841</v>
+      </c>
+      <c r="S24" s="8" t="n"/>
+      <c r="T24" s="8" t="n"/>
+      <c r="U24" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X24" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1268,29 +2181,72 @@
       <c r="B25" s="5" t="n">
         <v>43678</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="10" t="n">
+        <v>103.67</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>-0.016395</v>
+      </c>
+      <c r="E25" s="11" t="n">
         <v>3.162441</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="F25" s="10" t="n">
+        <v>104.005386</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>0.203268</v>
+      </c>
+      <c r="H25" s="11" t="n">
         <v>3.77672</v>
       </c>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="11" t="n">
+        <v>0.303801</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>3.761095</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>0.09464400000000001</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>3.793644</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>-0.700945</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>1.28267</v>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>-1.496182</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>2.783384</v>
+      </c>
+      <c r="Q25" s="11" t="n">
+        <v>-0.104838</v>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>0.201276</v>
+      </c>
+      <c r="S25" s="12" t="n"/>
+      <c r="T25" s="12" t="n"/>
+      <c r="U25" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X25" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1306,28 +2262,71 @@
         <v>43709</v>
       </c>
       <c r="C26" s="6" t="n">
+        <v>103.942</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0.262371</v>
+      </c>
+      <c r="E26" s="7" t="n">
         <v>2.997513</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="F26" s="6" t="n">
+        <v>104.315313</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0.297992</v>
+      </c>
+      <c r="H26" s="7" t="n">
         <v>3.75011</v>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="7" t="n">
+        <v>0.384681</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>3.765313</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>0.20413</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>3.733626</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.153213</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>0.705906</v>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>-0.024579</v>
+      </c>
+      <c r="P26" s="7" t="n">
+        <v>2.977587</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>0.284628</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>-0.904931</v>
+      </c>
+      <c r="S26" s="8" t="n"/>
+      <c r="T26" s="8" t="n"/>
+      <c r="U26" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V26" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X26" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1342,29 +2341,72 @@
       <c r="B27" s="5" t="n">
         <v>43739</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="10" t="n">
+        <v>104.503</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.539724</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>3.019519</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="F27" s="10" t="n">
+        <v>104.572028</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.246095</v>
+      </c>
+      <c r="H27" s="11" t="n">
         <v>3.683866</v>
       </c>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="11" t="n">
+        <v>0.256376</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>3.783288</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.234943</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>3.576216</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>1.461568</v>
+      </c>
+      <c r="N27" s="11" t="n">
+        <v>1.013175</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>0.108701</v>
+      </c>
+      <c r="P27" s="11" t="n">
+        <v>3.81829</v>
+      </c>
+      <c r="Q27" s="11" t="n">
+        <v>2.458464</v>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>-0.914376</v>
+      </c>
+      <c r="S27" s="12" t="n"/>
+      <c r="T27" s="12" t="n"/>
+      <c r="U27" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V27" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X27" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1380,28 +2422,71 @@
         <v>43770</v>
       </c>
       <c r="C28" s="6" t="n">
+        <v>105.346</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.806675</v>
+      </c>
+      <c r="E28" s="7" t="n">
         <v>2.974497</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="F28" s="6" t="n">
+        <v>104.803658</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0.221503</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <v>3.652655</v>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="n">
+        <v>0.119487</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>3.633781</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>0.332182</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>3.673095</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>2.619726</v>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>0.977089</v>
+      </c>
+      <c r="O28" s="7" t="n">
+        <v>1.844432</v>
+      </c>
+      <c r="P28" s="7" t="n">
+        <v>2.179321</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>3.177921</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>0.13975</v>
+      </c>
+      <c r="S28" s="8" t="n"/>
+      <c r="T28" s="8" t="n"/>
+      <c r="U28" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V28" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X28" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1416,29 +2501,72 @@
       <c r="B29" s="5" t="n">
         <v>43800</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="10" t="n">
+        <v>105.934</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.558161</v>
+      </c>
+      <c r="E29" s="11" t="n">
         <v>2.828577</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="F29" s="10" t="n">
+        <v>105.233794</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.410421</v>
+      </c>
+      <c r="H29" s="11" t="n">
         <v>3.594438</v>
       </c>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="11" t="n">
+        <v>0.263168</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>3.556448</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.569841</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>3.635473</v>
+      </c>
+      <c r="M29" s="11" t="n">
+        <v>1.002877</v>
+      </c>
+      <c r="N29" s="11" t="n">
+        <v>0.588384</v>
+      </c>
+      <c r="O29" s="11" t="n">
+        <v>1.776892</v>
+      </c>
+      <c r="P29" s="11" t="n">
+        <v>-0.033164</v>
+      </c>
+      <c r="Q29" s="11" t="n">
+        <v>0.452807</v>
+      </c>
+      <c r="R29" s="11" t="n">
+        <v>1.040732</v>
+      </c>
+      <c r="S29" s="12" t="n"/>
+      <c r="T29" s="12" t="n"/>
+      <c r="U29" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V29" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X29" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1454,28 +2582,71 @@
         <v>43831</v>
       </c>
       <c r="C30" s="6" t="n">
+        <v>106.447</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.484264</v>
+      </c>
+      <c r="E30" s="7" t="n">
         <v>3.238352</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="F30" s="6" t="n">
+        <v>105.577099</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="H30" s="7" t="n">
         <v>3.725805</v>
       </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="7" t="n">
+        <v>0.6611900000000001</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>3.923034</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>-0.035299</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>3.512296</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.961056</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>1.806218</v>
+      </c>
+      <c r="O30" s="7" t="n">
+        <v>1.829907</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>1.439153</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>0.335449</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v>2.076141</v>
+      </c>
+      <c r="S30" s="8" t="n"/>
+      <c r="T30" s="8" t="n"/>
+      <c r="U30" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V30" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X30" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1490,29 +2661,72 @@
       <c r="B31" s="5" t="n">
         <v>43862</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="10" t="n">
+        <v>106.889</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>3.696194</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="F31" s="10" t="n">
+        <v>105.96143</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>0.364029</v>
+      </c>
+      <c r="H31" s="11" t="n">
         <v>3.655943</v>
       </c>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="11" t="n">
+        <v>0.394897</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>3.821225</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>0.330482</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>3.47679</v>
+      </c>
+      <c r="M31" s="11" t="n">
+        <v>0.5669110000000001</v>
+      </c>
+      <c r="N31" s="11" t="n">
+        <v>3.813838</v>
+      </c>
+      <c r="O31" s="11" t="n">
+        <v>1.743618</v>
+      </c>
+      <c r="P31" s="11" t="n">
+        <v>7.820357</v>
+      </c>
+      <c r="Q31" s="11" t="n">
+        <v>-0.292985</v>
+      </c>
+      <c r="R31" s="11" t="n">
+        <v>1.014791</v>
+      </c>
+      <c r="S31" s="12" t="n"/>
+      <c r="T31" s="12" t="n"/>
+      <c r="U31" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V31" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X31" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1528,28 +2742,71 @@
         <v>43891</v>
       </c>
       <c r="C32" s="6" t="n">
+        <v>106.838</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>-0.047713</v>
+      </c>
+      <c r="E32" s="7" t="n">
         <v>3.249063</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="F32" s="6" t="n">
+        <v>106.272453</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0.293525</v>
+      </c>
+      <c r="H32" s="7" t="n">
         <v>3.603482</v>
       </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="7" t="n">
+        <v>0.353401</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>3.833094</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>0.228407</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>3.354611</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>-1.063905</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>2.191786</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>1.299431</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>9.958739</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>-2.826222</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>-3.127322</v>
+      </c>
+      <c r="S32" s="8" t="n"/>
+      <c r="T32" s="8" t="n"/>
+      <c r="U32" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V32" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X32" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1564,29 +2821,72 @@
       <c r="B33" s="5" t="n">
         <v>43922</v>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="10" t="n">
+        <v>105.755</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>-1.013684</v>
+      </c>
+      <c r="E33" s="11" t="n">
         <v>2.148149</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="F33" s="10" t="n">
+        <v>106.653927</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>0.358958</v>
+      </c>
+      <c r="H33" s="11" t="n">
         <v>3.504006</v>
       </c>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="11" t="n">
+        <v>0.634057</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>4.11332</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>0.059404</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>2.844846</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>-5.166697</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>-1.964219</v>
+      </c>
+      <c r="O33" s="11" t="n">
+        <v>-0.791664</v>
+      </c>
+      <c r="P33" s="11" t="n">
+        <v>8.516294</v>
+      </c>
+      <c r="Q33" s="11" t="n">
+        <v>-8.567629</v>
+      </c>
+      <c r="R33" s="11" t="n">
+        <v>-9.348801999999999</v>
+      </c>
+      <c r="S33" s="12" t="n"/>
+      <c r="T33" s="12" t="n"/>
+      <c r="U33" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V33" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X33" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1602,28 +2902,71 @@
         <v>43952</v>
       </c>
       <c r="C34" s="6" t="n">
+        <v>106.162</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0.384852</v>
+      </c>
+      <c r="E34" s="7" t="n">
         <v>2.837271</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="F34" s="6" t="n">
+        <v>106.97239</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0.298595</v>
+      </c>
+      <c r="H34" s="7" t="n">
         <v>3.643116</v>
       </c>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="n">
+        <v>0.464478</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>4.297728</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>0.116928</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>2.933142</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0.663365</v>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>0.350384</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>1.343058</v>
+      </c>
+      <c r="P34" s="7" t="n">
+        <v>9.787756</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>0.090071</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>-6.512675</v>
+      </c>
+      <c r="S34" s="8" t="n"/>
+      <c r="T34" s="8" t="n"/>
+      <c r="U34" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V34" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X34" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1638,29 +2981,72 @@
       <c r="B35" s="5" t="n">
         <v>43983</v>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C35" s="10" t="n">
+        <v>106.743</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>0.547277</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>3.334011</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="F35" s="10" t="n">
+        <v>107.365896</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>0.367858</v>
+      </c>
+      <c r="H35" s="11" t="n">
         <v>3.709552</v>
       </c>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="11" t="n">
+        <v>0.603763</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>4.685595</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>0.10861</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>2.652558</v>
+      </c>
+      <c r="M35" s="11" t="n">
+        <v>1.116028</v>
+      </c>
+      <c r="N35" s="11" t="n">
+        <v>2.161044</v>
+      </c>
+      <c r="O35" s="11" t="n">
+        <v>-2.08524</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>7.691594</v>
+      </c>
+      <c r="Q35" s="11" t="n">
+        <v>3.849974</v>
+      </c>
+      <c r="R35" s="11" t="n">
+        <v>-1.895759</v>
+      </c>
+      <c r="S35" s="12" t="n"/>
+      <c r="T35" s="12" t="n"/>
+      <c r="U35" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V35" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W35" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X35" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1676,28 +3062,71 @@
         <v>44013</v>
       </c>
       <c r="C36" s="6" t="n">
+        <v>107.444</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0.656718</v>
+      </c>
+      <c r="E36" s="7" t="n">
         <v>3.623405</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="F36" s="6" t="n">
+        <v>107.790972</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0.395913</v>
+      </c>
+      <c r="H36" s="7" t="n">
         <v>3.850464</v>
       </c>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="7" t="n">
+        <v>0.63672</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>5.193978</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>0.129969</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>2.398823</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>1.483461</v>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>2.917096</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>-0.032972</v>
+      </c>
+      <c r="P36" s="7" t="n">
+        <v>5.545873</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>2.704509</v>
+      </c>
+      <c r="R36" s="7" t="n">
+        <v>0.946576</v>
+      </c>
+      <c r="S36" s="8" t="n"/>
+      <c r="T36" s="8" t="n"/>
+      <c r="U36" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V36" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X36" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1712,29 +3141,72 @@
       <c r="B37" s="5" t="n">
         <v>44044</v>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="10" t="n">
+        <v>107.867</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>0.393693</v>
+      </c>
+      <c r="E37" s="11" t="n">
         <v>4.048423</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="F37" s="10" t="n">
+        <v>108.132454</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="H37" s="11" t="n">
         <v>3.968129</v>
       </c>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="11" t="n">
+        <v>0.465654</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>5.363723</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>0.151576</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>2.457066</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>0.63442</v>
+      </c>
+      <c r="N37" s="11" t="n">
+        <v>4.301115</v>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>0.881147</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>8.093157</v>
+      </c>
+      <c r="Q37" s="11" t="n">
+        <v>0.441047</v>
+      </c>
+      <c r="R37" s="11" t="n">
+        <v>1.498207</v>
+      </c>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="12" t="n"/>
+      <c r="U37" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V37" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W37" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X37" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1750,28 +3222,71 @@
         <v>44075</v>
       </c>
       <c r="C38" s="6" t="n">
+        <v>108.114</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0.228986</v>
+      </c>
+      <c r="E38" s="7" t="n">
         <v>4.013777</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="F38" s="6" t="n">
+        <v>108.473724</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0.315604</v>
+      </c>
+      <c r="H38" s="7" t="n">
         <v>3.986386</v>
       </c>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I38" s="7" t="n">
+        <v>0.419148</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>5.399899</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>0.200313</v>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>2.453163</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>-0.039358</v>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>4.100569</v>
+      </c>
+      <c r="O38" s="7" t="n">
+        <v>0.038314</v>
+      </c>
+      <c r="P38" s="7" t="n">
+        <v>8.161156</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>-0.1005</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>1.108418</v>
+      </c>
+      <c r="S38" s="8" t="n"/>
+      <c r="T38" s="8" t="n"/>
+      <c r="U38" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V38" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X38" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1786,29 +3301,72 @@
       <c r="B39" s="5" t="n">
         <v>44105</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="10" t="n">
+        <v>108.774</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>0.610467</v>
+      </c>
+      <c r="E39" s="11" t="n">
         <v>4.086964</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="F39" s="10" t="n">
+        <v>108.733448</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>0.239434</v>
+      </c>
+      <c r="H39" s="11" t="n">
         <v>3.979477</v>
       </c>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="11" t="n">
+        <v>0.292831</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>5.438224</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>0.17985</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>2.396851</v>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>1.772944</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>4.420044</v>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>1.451447</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>9.611908</v>
+      </c>
+      <c r="Q39" s="11" t="n">
+        <v>2.026373</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>0.68202</v>
+      </c>
+      <c r="S39" s="12" t="n"/>
+      <c r="T39" s="12" t="n"/>
+      <c r="U39" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V39" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X39" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1824,28 +3382,71 @@
         <v>44136</v>
       </c>
       <c r="C40" s="6" t="n">
+        <v>108.856</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0.07538599999999999</v>
+      </c>
+      <c r="E40" s="7" t="n">
         <v>3.331878</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="F40" s="6" t="n">
+        <v>108.641831</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>-0.084258</v>
+      </c>
+      <c r="H40" s="7" t="n">
         <v>3.662251</v>
       </c>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="7" t="n">
+        <v>-0.306217</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>4.989904</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>0.163703</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>2.224905</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>0.564846</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>2.329114</v>
+      </c>
+      <c r="O40" s="7" t="n">
+        <v>-0.396947</v>
+      </c>
+      <c r="P40" s="7" t="n">
+        <v>7.199584</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>1.318733</v>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>-1.132192</v>
+      </c>
+      <c r="S40" s="8" t="n"/>
+      <c r="T40" s="8" t="n"/>
+      <c r="U40" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V40" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X40" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1860,29 +3461,72 @@
       <c r="B41" s="5" t="n">
         <v>44166</v>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C41" s="10" t="n">
+        <v>109.271</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>0.381238</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <v>3.150075</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="F41" s="10" t="n">
+        <v>109.236711</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>0.54756</v>
+      </c>
+      <c r="H41" s="11" t="n">
         <v>3.803832</v>
       </c>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="11" t="n">
+        <v>0.770093</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>5.520728</v>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>0.300125</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>1.95075</v>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>-0.127271</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>1.184126</v>
+      </c>
+      <c r="O41" s="11" t="n">
+        <v>-1.30057</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>3.958155</v>
+      </c>
+      <c r="Q41" s="11" t="n">
+        <v>0.776827</v>
+      </c>
+      <c r="R41" s="11" t="n">
+        <v>-0.813284</v>
+      </c>
+      <c r="S41" s="12" t="n"/>
+      <c r="T41" s="12" t="n"/>
+      <c r="U41" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V41" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X41" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1898,28 +3542,71 @@
         <v>44197</v>
       </c>
       <c r="C42" s="6" t="n">
+        <v>110.21</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0.859331</v>
+      </c>
+      <c r="E42" s="7" t="n">
         <v>3.535093</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="F42" s="6" t="n">
+        <v>109.628897</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0.359024</v>
+      </c>
+      <c r="H42" s="7" t="n">
         <v>3.837762</v>
       </c>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I42" s="7" t="n">
+        <v>0.551018</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>5.405237</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>0.144544</v>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>2.134167</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>2.40415</v>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>2.630409</v>
+      </c>
+      <c r="O42" s="7" t="n">
+        <v>0.538579</v>
+      </c>
+      <c r="P42" s="7" t="n">
+        <v>2.639838</v>
+      </c>
+      <c r="Q42" s="7" t="n">
+        <v>3.812054</v>
+      </c>
+      <c r="R42" s="7" t="n">
+        <v>2.623518</v>
+      </c>
+      <c r="S42" s="8" t="n"/>
+      <c r="T42" s="8" t="n"/>
+      <c r="U42" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V42" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X42" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1934,29 +3621,72 @@
       <c r="B43" s="5" t="n">
         <v>44228</v>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C43" s="10" t="n">
+        <v>110.907</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>0.632429</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <v>3.75904</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="F43" s="10" t="n">
+        <v>110.060903</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>0.394062</v>
+      </c>
+      <c r="H43" s="11" t="n">
         <v>3.868835</v>
       </c>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="11" t="n">
+        <v>0.5187079999999999</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>5.535228</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>0.254253</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>2.056568</v>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>1.355032</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>3.434701</v>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>-0.217652</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>0.661292</v>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>2.504476</v>
+      </c>
+      <c r="R43" s="11" t="n">
+        <v>5.502806</v>
+      </c>
+      <c r="S43" s="12" t="n"/>
+      <c r="T43" s="12" t="n"/>
+      <c r="U43" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V43" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X43" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -1972,28 +3702,71 @@
         <v>44256</v>
       </c>
       <c r="C44" s="6" t="n">
+        <v>111.824</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0.826819</v>
+      </c>
+      <c r="E44" s="7" t="n">
         <v>4.666879</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="F44" s="6" t="n">
+        <v>110.653978</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0.538861</v>
+      </c>
+      <c r="H44" s="7" t="n">
         <v>4.122917</v>
       </c>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I44" s="7" t="n">
+        <v>0.598457</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>5.792938</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>0.471839</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>2.30444</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>1.689706</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>6.313518</v>
+      </c>
+      <c r="O44" s="7" t="n">
+        <v>1.27341</v>
+      </c>
+      <c r="P44" s="7" t="n">
+        <v>0.635435</v>
+      </c>
+      <c r="Q44" s="7" t="n">
+        <v>1.985889</v>
+      </c>
+      <c r="R44" s="7" t="n">
+        <v>10.727376</v>
+      </c>
+      <c r="S44" s="8" t="n"/>
+      <c r="T44" s="8" t="n"/>
+      <c r="U44" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V44" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X44" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2008,29 +3781,72 @@
       <c r="B45" s="5" t="n">
         <v>44287</v>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="10" t="n">
+        <v>112.19</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="E45" s="11" t="n">
         <v>6.084819</v>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="F45" s="10" t="n">
+        <v>111.060931</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="H45" s="11" t="n">
         <v>4.13206</v>
       </c>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I45" s="11" t="n">
+        <v>0.444348</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>5.593503</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>0.281542</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>2.531562</v>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>0.205998</v>
+      </c>
+      <c r="N45" s="11" t="n">
+        <v>12.336613</v>
+      </c>
+      <c r="O45" s="11" t="n">
+        <v>2.607379</v>
+      </c>
+      <c r="P45" s="11" t="n">
+        <v>4.083372</v>
+      </c>
+      <c r="Q45" s="11" t="n">
+        <v>-1.49058</v>
+      </c>
+      <c r="R45" s="11" t="n">
+        <v>19.297898</v>
+      </c>
+      <c r="S45" s="12" t="n"/>
+      <c r="T45" s="12" t="n"/>
+      <c r="U45" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V45" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X45" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2046,28 +3862,71 @@
         <v>44317</v>
       </c>
       <c r="C46" s="6" t="n">
+        <v>112.419</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0.204118</v>
+      </c>
+      <c r="E46" s="7" t="n">
         <v>5.893823</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="F46" s="6" t="n">
+        <v>111.644223</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="H46" s="7" t="n">
         <v>4.367326</v>
       </c>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="n">
+        <v>0.619468</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>5.756406</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>2.840796</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>-0.748524</v>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>10.760997</v>
+      </c>
+      <c r="O46" s="7" t="n">
+        <v>1.911554</v>
+      </c>
+      <c r="P46" s="7" t="n">
+        <v>4.667241</v>
+      </c>
+      <c r="Q46" s="7" t="n">
+        <v>-2.706051</v>
+      </c>
+      <c r="R46" s="7" t="n">
+        <v>15.965184</v>
+      </c>
+      <c r="S46" s="8" t="n"/>
+      <c r="T46" s="8" t="n"/>
+      <c r="U46" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V46" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X46" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2082,29 +3941,72 @@
       <c r="B47" s="5" t="n">
         <v>44348</v>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C47" s="10" t="n">
+        <v>113.018</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0.532828</v>
+      </c>
+      <c r="E47" s="11" t="n">
         <v>5.878606</v>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="F47" s="10" t="n">
+        <v>112.281133</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>0.570482</v>
+      </c>
+      <c r="H47" s="11" t="n">
         <v>4.578025</v>
       </c>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+      <c r="I47" s="11" t="n">
+        <v>0.650425</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>5.805458</v>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>0.480139</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>3.222465</v>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>0.418514</v>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>9.996950999999999</v>
+      </c>
+      <c r="O47" s="11" t="n">
+        <v>0.046762</v>
+      </c>
+      <c r="P47" s="11" t="n">
+        <v>6.946272</v>
+      </c>
+      <c r="Q47" s="11" t="n">
+        <v>0.705067</v>
+      </c>
+      <c r="R47" s="11" t="n">
+        <v>12.45339</v>
+      </c>
+      <c r="S47" s="12" t="n"/>
+      <c r="T47" s="12" t="n"/>
+      <c r="U47" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V47" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X47" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2120,28 +4022,71 @@
         <v>44378</v>
       </c>
       <c r="C48" s="6" t="n">
+        <v>113.682</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0.587517</v>
+      </c>
+      <c r="E48" s="7" t="n">
         <v>5.805815</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="F48" s="6" t="n">
+        <v>112.815077</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0.475542</v>
+      </c>
+      <c r="H48" s="7" t="n">
         <v>4.66097</v>
       </c>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I48" s="7" t="n">
+        <v>0.575232</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>5.740813</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>3.462372</v>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>0.9270659999999999</v>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>9.393879999999999</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0.738729</v>
+      </c>
+      <c r="P48" s="7" t="n">
+        <v>7.77185</v>
+      </c>
+      <c r="Q48" s="7" t="n">
+        <v>1.07129</v>
+      </c>
+      <c r="R48" s="7" t="n">
+        <v>10.665144</v>
+      </c>
+      <c r="S48" s="8" t="n"/>
+      <c r="T48" s="8" t="n"/>
+      <c r="U48" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V48" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X48" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2156,29 +4101,72 @@
       <c r="B49" s="5" t="n">
         <v>44409</v>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C49" s="10" t="n">
+        <v>113.899</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>0.190883</v>
+      </c>
+      <c r="E49" s="11" t="n">
         <v>5.592072</v>
       </c>
-      <c r="D49" s="8" t="n">
+      <c r="F49" s="10" t="n">
+        <v>113.296654</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>0.426873</v>
+      </c>
+      <c r="H49" s="11" t="n">
         <v>4.77581</v>
       </c>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="I49" s="11" t="n">
+        <v>0.7005479999999999</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>5.98804</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>0.116411</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>3.426045</v>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>-0.519436</v>
+      </c>
+      <c r="N49" s="11" t="n">
+        <v>8.13959</v>
+      </c>
+      <c r="O49" s="11" t="n">
+        <v>1.982343</v>
+      </c>
+      <c r="P49" s="11" t="n">
+        <v>8.948263000000001</v>
+      </c>
+      <c r="Q49" s="11" t="n">
+        <v>-2.428939</v>
+      </c>
+      <c r="R49" s="11" t="n">
+        <v>7.503016</v>
+      </c>
+      <c r="S49" s="12" t="n"/>
+      <c r="T49" s="12" t="n"/>
+      <c r="U49" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V49" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W49" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X49" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2194,28 +4182,71 @@
         <v>44440</v>
       </c>
       <c r="C50" s="6" t="n">
+        <v>114.601</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0.616336</v>
+      </c>
+      <c r="E50" s="7" t="n">
         <v>6.000148</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="F50" s="6" t="n">
+        <v>113.815393</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0.457859</v>
+      </c>
+      <c r="H50" s="7" t="n">
         <v>4.92439</v>
       </c>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="7" t="n">
+        <v>0.676726</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>6.259903</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0.208124</v>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>3.434107</v>
+      </c>
+      <c r="M50" s="7" t="n">
+        <v>1.098398</v>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>9.370438</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>1.379356</v>
+      </c>
+      <c r="P50" s="7" t="n">
+        <v>10.408746</v>
+      </c>
+      <c r="Q50" s="7" t="n">
+        <v>0.874259</v>
+      </c>
+      <c r="R50" s="7" t="n">
+        <v>8.551964999999999</v>
+      </c>
+      <c r="S50" s="8" t="n"/>
+      <c r="T50" s="8" t="n"/>
+      <c r="U50" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V50" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X50" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2230,29 +4261,72 @@
       <c r="B51" s="5" t="n">
         <v>44470</v>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C51" s="10" t="n">
+        <v>115.561</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>0.837689</v>
+      </c>
+      <c r="E51" s="11" t="n">
         <v>6.239543</v>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="F51" s="10" t="n">
+        <v>114.377964</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>0.494284</v>
+      </c>
+      <c r="H51" s="11" t="n">
         <v>5.19115</v>
       </c>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="I51" s="11" t="n">
+        <v>0.595988</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>6.581096</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>0.377694</v>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>3.638377</v>
+      </c>
+      <c r="M51" s="11" t="n">
+        <v>1.868283</v>
+      </c>
+      <c r="N51" s="11" t="n">
+        <v>9.472894999999999</v>
+      </c>
+      <c r="O51" s="11" t="n">
+        <v>0.179571</v>
+      </c>
+      <c r="P51" s="11" t="n">
+        <v>9.024575</v>
+      </c>
+      <c r="Q51" s="11" t="n">
+        <v>3.222224</v>
+      </c>
+      <c r="R51" s="11" t="n">
+        <v>9.824303</v>
+      </c>
+      <c r="S51" s="12" t="n"/>
+      <c r="T51" s="12" t="n"/>
+      <c r="U51" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V51" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W51" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X51" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2268,28 +4342,71 @@
         <v>44501</v>
       </c>
       <c r="C52" s="6" t="n">
+        <v>116.884</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>1.14485</v>
+      </c>
+      <c r="E52" s="7" t="n">
         <v>7.374881</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="F52" s="6" t="n">
+        <v>114.799064</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>0.368165</v>
+      </c>
+      <c r="H52" s="7" t="n">
         <v>5.66746</v>
       </c>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="7" t="n">
+        <v>0.313114</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>7.243214</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>0.43141</v>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>3.915372</v>
+      </c>
+      <c r="M52" s="7" t="n">
+        <v>3.447887</v>
+      </c>
+      <c r="N52" s="7" t="n">
+        <v>12.611316</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>4.480507</v>
+      </c>
+      <c r="P52" s="7" t="n">
+        <v>14.363391</v>
+      </c>
+      <c r="Q52" s="7" t="n">
+        <v>2.644378</v>
+      </c>
+      <c r="R52" s="7" t="n">
+        <v>11.261234</v>
+      </c>
+      <c r="S52" s="8" t="n"/>
+      <c r="T52" s="8" t="n"/>
+      <c r="U52" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V52" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X52" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2304,29 +4421,72 @@
       <c r="B53" s="5" t="n">
         <v>44531</v>
       </c>
-      <c r="C53" s="8" t="n">
+      <c r="C53" s="10" t="n">
+        <v>117.308</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>0.362753</v>
+      </c>
+      <c r="E53" s="11" t="n">
         <v>7.355108</v>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="F53" s="10" t="n">
+        <v>115.720705</v>
+      </c>
+      <c r="G53" s="11" t="n">
+        <v>0.80283</v>
+      </c>
+      <c r="H53" s="11" t="n">
         <v>5.935728</v>
       </c>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="I53" s="11" t="n">
+        <v>0.913631</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>7.395972</v>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>0.675686</v>
+      </c>
+      <c r="L53" s="11" t="n">
+        <v>4.304469</v>
+      </c>
+      <c r="M53" s="11" t="n">
+        <v>-0.904053</v>
+      </c>
+      <c r="N53" s="11" t="n">
+        <v>11.735457</v>
+      </c>
+      <c r="O53" s="11" t="n">
+        <v>-0.075727</v>
+      </c>
+      <c r="P53" s="11" t="n">
+        <v>15.782621</v>
+      </c>
+      <c r="Q53" s="11" t="n">
+        <v>-1.560125</v>
+      </c>
+      <c r="R53" s="11" t="n">
+        <v>8.681153999999999</v>
+      </c>
+      <c r="S53" s="12" t="n"/>
+      <c r="T53" s="12" t="n"/>
+      <c r="U53" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V53" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W53" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X53" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2342,28 +4502,71 @@
         <v>44562</v>
       </c>
       <c r="C54" s="6" t="n">
+        <v>118.002</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0.591605</v>
+      </c>
+      <c r="E54" s="7" t="n">
         <v>7.070139</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="F54" s="6" t="n">
+        <v>116.432721</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>0.6152879999999999</v>
+      </c>
+      <c r="H54" s="7" t="n">
         <v>6.206233</v>
       </c>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="7" t="n">
+        <v>0.9888169999999999</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>7.863573</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>0.185647</v>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>4.347279</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0.522629</v>
+      </c>
+      <c r="N54" s="7" t="n">
+        <v>9.682487999999999</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0.138233</v>
+      </c>
+      <c r="P54" s="7" t="n">
+        <v>15.321573</v>
+      </c>
+      <c r="Q54" s="7" t="n">
+        <v>0.83168</v>
+      </c>
+      <c r="R54" s="7" t="n">
+        <v>5.560991</v>
+      </c>
+      <c r="S54" s="8" t="n"/>
+      <c r="T54" s="8" t="n"/>
+      <c r="U54" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V54" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X54" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2378,29 +4581,72 @@
       <c r="B55" s="5" t="n">
         <v>44593</v>
       </c>
-      <c r="C55" s="8" t="n">
+      <c r="C55" s="10" t="n">
+        <v>118.981</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>0.829647</v>
+      </c>
+      <c r="E55" s="11" t="n">
         <v>7.279973</v>
       </c>
-      <c r="D55" s="8" t="n">
+      <c r="F55" s="10" t="n">
+        <v>117.316585</v>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>0.75912</v>
+      </c>
+      <c r="H55" s="11" t="n">
         <v>6.592425</v>
       </c>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="I55" s="11" t="n">
+        <v>0.964592</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>8.342036999999999</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>0.520886</v>
+      </c>
+      <c r="L55" s="11" t="n">
+        <v>4.624798</v>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>1.036169</v>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>9.337427</v>
+      </c>
+      <c r="O55" s="11" t="n">
+        <v>0.515043</v>
+      </c>
+      <c r="P55" s="11" t="n">
+        <v>16.168371</v>
+      </c>
+      <c r="Q55" s="11" t="n">
+        <v>1.452268</v>
+      </c>
+      <c r="R55" s="11" t="n">
+        <v>4.477408</v>
+      </c>
+      <c r="S55" s="12" t="n"/>
+      <c r="T55" s="12" t="n"/>
+      <c r="U55" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V55" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W55" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X55" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2416,28 +4662,71 @@
         <v>44621</v>
       </c>
       <c r="C56" s="6" t="n">
+        <v>120.159</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0.990074</v>
+      </c>
+      <c r="E56" s="7" t="n">
         <v>7.453677</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="F56" s="6" t="n">
+        <v>118.155869</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>0.715401</v>
+      </c>
+      <c r="H56" s="7" t="n">
         <v>6.779595</v>
       </c>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="7" t="n">
+        <v>0.926045</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>8.694839999999999</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>0.470093</v>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>4.62298</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>1.793782</v>
+      </c>
+      <c r="N56" s="7" t="n">
+        <v>9.44933</v>
+      </c>
+      <c r="O56" s="7" t="n">
+        <v>1.233957</v>
+      </c>
+      <c r="P56" s="7" t="n">
+        <v>16.123115</v>
+      </c>
+      <c r="Q56" s="7" t="n">
+        <v>2.23665</v>
+      </c>
+      <c r="R56" s="7" t="n">
+        <v>4.734296</v>
+      </c>
+      <c r="S56" s="8" t="n"/>
+      <c r="T56" s="8" t="n"/>
+      <c r="U56" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V56" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X56" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2452,29 +4741,72 @@
       <c r="B57" s="5" t="n">
         <v>44652</v>
       </c>
-      <c r="C57" s="8" t="n">
+      <c r="C57" s="10" t="n">
+        <v>120.809</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>0.54095</v>
+      </c>
+      <c r="E57" s="11" t="n">
         <v>7.682503</v>
       </c>
-      <c r="D57" s="8" t="n">
+      <c r="F57" s="10" t="n">
+        <v>119.074242</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>0.777255</v>
+      </c>
+      <c r="H57" s="11" t="n">
         <v>7.215239</v>
       </c>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="I57" s="11" t="n">
+        <v>1.027658</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>9.326063</v>
+      </c>
+      <c r="K57" s="11" t="n">
+        <v>0.484322</v>
+      </c>
+      <c r="L57" s="11" t="n">
+        <v>4.834539</v>
+      </c>
+      <c r="M57" s="11" t="n">
+        <v>-0.141218</v>
+      </c>
+      <c r="N57" s="11" t="n">
+        <v>9.070086</v>
+      </c>
+      <c r="O57" s="11" t="n">
+        <v>1.045809</v>
+      </c>
+      <c r="P57" s="11" t="n">
+        <v>14.355851</v>
+      </c>
+      <c r="Q57" s="11" t="n">
+        <v>-1.071046</v>
+      </c>
+      <c r="R57" s="11" t="n">
+        <v>5.18034</v>
+      </c>
+      <c r="S57" s="12" t="n"/>
+      <c r="T57" s="12" t="n"/>
+      <c r="U57" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V57" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W57" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X57" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2490,28 +4822,71 @@
         <v>44682</v>
       </c>
       <c r="C58" s="6" t="n">
+        <v>121.022</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.176311</v>
+      </c>
+      <c r="E58" s="7" t="n">
         <v>7.652621</v>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="F58" s="6" t="n">
+        <v>119.774026</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>0.587687</v>
+      </c>
+      <c r="H58" s="7" t="n">
         <v>7.281884</v>
       </c>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="7" t="n">
+        <v>0.8085329999999999</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>9.531489000000001</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>0.327933</v>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>4.739592</v>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>-1.024816</v>
+      </c>
+      <c r="N58" s="7" t="n">
+        <v>8.766461</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0.776145</v>
+      </c>
+      <c r="P58" s="7" t="n">
+        <v>13.081798</v>
+      </c>
+      <c r="Q58" s="7" t="n">
+        <v>-2.465742</v>
+      </c>
+      <c r="R58" s="7" t="n">
+        <v>5.440128</v>
+      </c>
+      <c r="S58" s="8" t="n"/>
+      <c r="T58" s="8" t="n"/>
+      <c r="U58" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V58" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X58" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2526,29 +4901,72 @@
       <c r="B59" s="5" t="n">
         <v>44713</v>
       </c>
-      <c r="C59" s="8" t="n">
+      <c r="C59" s="10" t="n">
+        <v>122.044</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>0.844475</v>
+      </c>
+      <c r="E59" s="11" t="n">
         <v>7.986338</v>
       </c>
-      <c r="D59" s="8" t="n">
+      <c r="F59" s="10" t="n">
+        <v>120.696376</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>0.770075</v>
+      </c>
+      <c r="H59" s="11" t="n">
         <v>7.494796</v>
       </c>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I59" s="11" t="n">
+        <v>1.001752</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>9.913816000000001</v>
+      </c>
+      <c r="K59" s="11" t="n">
+        <v>0.496277</v>
+      </c>
+      <c r="L59" s="11" t="n">
+        <v>4.756415</v>
+      </c>
+      <c r="M59" s="11" t="n">
+        <v>1.066628</v>
+      </c>
+      <c r="N59" s="11" t="n">
+        <v>9.468453999999999</v>
+      </c>
+      <c r="O59" s="11" t="n">
+        <v>1.758181</v>
+      </c>
+      <c r="P59" s="11" t="n">
+        <v>15.016196</v>
+      </c>
+      <c r="Q59" s="11" t="n">
+        <v>0.494935</v>
+      </c>
+      <c r="R59" s="11" t="n">
+        <v>5.220116</v>
+      </c>
+      <c r="S59" s="12" t="n"/>
+      <c r="T59" s="12" t="n"/>
+      <c r="U59" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V59" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W59" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X59" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2564,28 +4982,71 @@
         <v>44743</v>
       </c>
       <c r="C60" s="6" t="n">
+        <v>122.948</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0.740716</v>
+      </c>
+      <c r="E60" s="7" t="n">
         <v>8.150807</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="F60" s="6" t="n">
+        <v>121.447327</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>0.622182</v>
+      </c>
+      <c r="H60" s="7" t="n">
         <v>7.651681</v>
       </c>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="I60" s="7" t="n">
+        <v>0.722496</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>10.074753</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>0.503034</v>
+      </c>
+      <c r="L60" s="7" t="n">
+        <v>4.902903</v>
+      </c>
+      <c r="M60" s="7" t="n">
+        <v>1.090195</v>
+      </c>
+      <c r="N60" s="7" t="n">
+        <v>9.645388000000001</v>
+      </c>
+      <c r="O60" s="7" t="n">
+        <v>1.642045</v>
+      </c>
+      <c r="P60" s="7" t="n">
+        <v>16.047537</v>
+      </c>
+      <c r="Q60" s="7" t="n">
+        <v>0.628256</v>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>4.758897</v>
+      </c>
+      <c r="S60" s="8" t="n"/>
+      <c r="T60" s="8" t="n"/>
+      <c r="U60" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V60" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X60" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2600,29 +5061,72 @@
       <c r="B61" s="5" t="n">
         <v>44774</v>
       </c>
-      <c r="C61" s="8" t="n">
+      <c r="C61" s="10" t="n">
+        <v>123.803</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>0.695416</v>
+      </c>
+      <c r="E61" s="11" t="n">
         <v>8.695423</v>
       </c>
-      <c r="D61" s="8" t="n">
+      <c r="F61" s="10" t="n">
+        <v>122.417294</v>
+      </c>
+      <c r="G61" s="11" t="n">
+        <v>0.798673</v>
+      </c>
+      <c r="H61" s="11" t="n">
         <v>8.050229</v>
       </c>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
+      <c r="I61" s="11" t="n">
+        <v>1.138487</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>10.55346</v>
+      </c>
+      <c r="K61" s="11" t="n">
+        <v>0.394175</v>
+      </c>
+      <c r="L61" s="11" t="n">
+        <v>5.193948</v>
+      </c>
+      <c r="M61" s="11" t="n">
+        <v>0.389342</v>
+      </c>
+      <c r="N61" s="11" t="n">
+        <v>10.647024</v>
+      </c>
+      <c r="O61" s="11" t="n">
+        <v>0.9754969999999999</v>
+      </c>
+      <c r="P61" s="11" t="n">
+        <v>14.901829</v>
+      </c>
+      <c r="Q61" s="11" t="n">
+        <v>-0.106255</v>
+      </c>
+      <c r="R61" s="11" t="n">
+        <v>7.252687</v>
+      </c>
+      <c r="S61" s="12" t="n"/>
+      <c r="T61" s="12" t="n"/>
+      <c r="U61" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V61" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W61" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X61" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2638,28 +5142,71 @@
         <v>44805</v>
       </c>
       <c r="C62" s="6" t="n">
+        <v>124.571</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0.62034</v>
+      </c>
+      <c r="E62" s="7" t="n">
         <v>8.69975</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="F62" s="6" t="n">
+        <v>123.239175</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>0.671377</v>
+      </c>
+      <c r="H62" s="7" t="n">
         <v>8.279883999999999</v>
       </c>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I62" s="7" t="n">
+        <v>0.936003</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>10.838173</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>0.354046</v>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>5.34713</v>
+      </c>
+      <c r="M62" s="7" t="n">
+        <v>0.472408</v>
+      </c>
+      <c r="N62" s="7" t="n">
+        <v>9.961911000000001</v>
+      </c>
+      <c r="O62" s="7" t="n">
+        <v>1.511896</v>
+      </c>
+      <c r="P62" s="7" t="n">
+        <v>15.052048</v>
+      </c>
+      <c r="Q62" s="7" t="n">
+        <v>-0.416002</v>
+      </c>
+      <c r="R62" s="7" t="n">
+        <v>5.880841</v>
+      </c>
+      <c r="S62" s="8" t="n"/>
+      <c r="T62" s="8" t="n"/>
+      <c r="U62" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V62" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X62" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2674,29 +5221,72 @@
       <c r="B63" s="5" t="n">
         <v>44835</v>
       </c>
-      <c r="C63" s="8" t="n">
+      <c r="C63" s="10" t="n">
+        <v>125.276</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>0.5659419999999999</v>
+      </c>
+      <c r="E63" s="11" t="n">
         <v>8.406815</v>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="F63" s="10" t="n">
+        <v>124.013219</v>
+      </c>
+      <c r="G63" s="11" t="n">
+        <v>0.628082</v>
+      </c>
+      <c r="H63" s="11" t="n">
         <v>8.424048000000001</v>
       </c>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="I63" s="11" t="n">
+        <v>0.874775</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>11.145345</v>
+      </c>
+      <c r="K63" s="11" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="L63" s="11" t="n">
+        <v>5.297641</v>
+      </c>
+      <c r="M63" s="11" t="n">
+        <v>0.381391</v>
+      </c>
+      <c r="N63" s="11" t="n">
+        <v>8.356882000000001</v>
+      </c>
+      <c r="O63" s="11" t="n">
+        <v>-0.519997</v>
+      </c>
+      <c r="P63" s="11" t="n">
+        <v>14.248622</v>
+      </c>
+      <c r="Q63" s="11" t="n">
+        <v>1.166687</v>
+      </c>
+      <c r="R63" s="11" t="n">
+        <v>3.772361</v>
+      </c>
+      <c r="S63" s="12" t="n"/>
+      <c r="T63" s="12" t="n"/>
+      <c r="U63" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V63" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W63" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X63" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2712,28 +5302,71 @@
         <v>44866</v>
       </c>
       <c r="C64" s="6" t="n">
+        <v>125.997</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>0.575529</v>
+      </c>
+      <c r="E64" s="7" t="n">
         <v>7.796619</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="F64" s="6" t="n">
+        <v>124.574021</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>0.452212</v>
+      </c>
+      <c r="H64" s="7" t="n">
         <v>8.514841000000001</v>
       </c>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I64" s="7" t="n">
+        <v>0.431234</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>11.276219</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>0.477651</v>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>5.346123</v>
+      </c>
+      <c r="M64" s="7" t="n">
+        <v>0.941841</v>
+      </c>
+      <c r="N64" s="7" t="n">
+        <v>5.731915</v>
+      </c>
+      <c r="O64" s="7" t="n">
+        <v>-0.417386</v>
+      </c>
+      <c r="P64" s="7" t="n">
+        <v>8.892815000000001</v>
+      </c>
+      <c r="Q64" s="7" t="n">
+        <v>2.106266</v>
+      </c>
+      <c r="R64" s="7" t="n">
+        <v>3.228336</v>
+      </c>
+      <c r="S64" s="8" t="n"/>
+      <c r="T64" s="8" t="n"/>
+      <c r="U64" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V64" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X64" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2748,29 +5381,72 @@
       <c r="B65" s="5" t="n">
         <v>44896</v>
       </c>
-      <c r="C65" s="8" t="n">
+      <c r="C65" s="10" t="n">
+        <v>126.478</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>0.381755</v>
+      </c>
+      <c r="E65" s="11" t="n">
         <v>7.817029</v>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="F65" s="10" t="n">
+        <v>125.378874</v>
+      </c>
+      <c r="G65" s="11" t="n">
+        <v>0.646084</v>
+      </c>
+      <c r="H65" s="11" t="n">
         <v>8.346102</v>
       </c>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I65" s="11" t="n">
+        <v>0.740849</v>
+      </c>
+      <c r="J65" s="11" t="n">
+        <v>11.085695</v>
+      </c>
+      <c r="K65" s="11" t="n">
+        <v>0.531218</v>
+      </c>
+      <c r="L65" s="11" t="n">
+        <v>5.194953</v>
+      </c>
+      <c r="M65" s="11" t="n">
+        <v>-0.400025</v>
+      </c>
+      <c r="N65" s="11" t="n">
+        <v>6.269695</v>
+      </c>
+      <c r="O65" s="11" t="n">
+        <v>0.5013069999999999</v>
+      </c>
+      <c r="P65" s="11" t="n">
+        <v>9.521639</v>
+      </c>
+      <c r="Q65" s="11" t="n">
+        <v>-1.153096</v>
+      </c>
+      <c r="R65" s="11" t="n">
+        <v>3.655165</v>
+      </c>
+      <c r="S65" s="12" t="n"/>
+      <c r="T65" s="12" t="n"/>
+      <c r="U65" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V65" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W65" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X65" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2786,28 +5462,71 @@
         <v>44927</v>
       </c>
       <c r="C66" s="6" t="n">
+        <v>127.336</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0.678379</v>
+      </c>
+      <c r="E66" s="7" t="n">
         <v>7.910035</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="F66" s="6" t="n">
+        <v>126.275085</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>0.714802</v>
+      </c>
+      <c r="H66" s="7" t="n">
         <v>8.453262</v>
       </c>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
+      <c r="I66" s="7" t="n">
+        <v>0.906635</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>10.995296</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>0.481796</v>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>5.50591</v>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>0.570804</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>6.320623</v>
+      </c>
+      <c r="O66" s="7" t="n">
+        <v>0.5101869999999999</v>
+      </c>
+      <c r="P66" s="7" t="n">
+        <v>9.928447</v>
+      </c>
+      <c r="Q66" s="7" t="n">
+        <v>0.622297</v>
+      </c>
+      <c r="R66" s="7" t="n">
+        <v>3.439918</v>
+      </c>
+      <c r="S66" s="8" t="n"/>
+      <c r="T66" s="8" t="n"/>
+      <c r="U66" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V66" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W66" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X66" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2822,29 +5541,72 @@
       <c r="B67" s="5" t="n">
         <v>44958</v>
       </c>
-      <c r="C67" s="8" t="n">
+      <c r="C67" s="10" t="n">
+        <v>128.046</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>0.55758</v>
+      </c>
+      <c r="E67" s="11" t="n">
         <v>7.618864</v>
       </c>
-      <c r="D67" s="8" t="n">
+      <c r="F67" s="10" t="n">
+        <v>127.046512</v>
+      </c>
+      <c r="G67" s="11" t="n">
+        <v>0.610911</v>
+      </c>
+      <c r="H67" s="11" t="n">
         <v>8.293735</v>
       </c>
-      <c r="E67" s="8" t="n"/>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
+      <c r="I67" s="11" t="n">
+        <v>0.650091</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>10.649551</v>
+      </c>
+      <c r="K67" s="11" t="n">
+        <v>0.563119</v>
+      </c>
+      <c r="L67" s="11" t="n">
+        <v>5.550237</v>
+      </c>
+      <c r="M67" s="11" t="n">
+        <v>0.398463</v>
+      </c>
+      <c r="N67" s="11" t="n">
+        <v>5.649564</v>
+      </c>
+      <c r="O67" s="11" t="n">
+        <v>-0.069673</v>
+      </c>
+      <c r="P67" s="11" t="n">
+        <v>9.288971999999999</v>
+      </c>
+      <c r="Q67" s="11" t="n">
+        <v>0.795699</v>
+      </c>
+      <c r="R67" s="11" t="n">
+        <v>2.770485</v>
+      </c>
+      <c r="S67" s="12" t="n"/>
+      <c r="T67" s="12" t="n"/>
+      <c r="U67" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V67" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W67" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X67" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2860,28 +5622,71 @@
         <v>44986</v>
       </c>
       <c r="C68" s="6" t="n">
+        <v>128.389</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0.267872</v>
+      </c>
+      <c r="E68" s="7" t="n">
         <v>6.849258</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="F68" s="6" t="n">
+        <v>127.712394</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>0.524124</v>
+      </c>
+      <c r="H68" s="7" t="n">
         <v>8.088066</v>
       </c>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="I68" s="7" t="n">
+        <v>0.446069</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>10.123333</v>
+      </c>
+      <c r="K68" s="7" t="n">
+        <v>0.619416</v>
+      </c>
+      <c r="L68" s="7" t="n">
+        <v>5.70711</v>
+      </c>
+      <c r="M68" s="7" t="n">
+        <v>-0.5005230000000001</v>
+      </c>
+      <c r="N68" s="7" t="n">
+        <v>3.268355</v>
+      </c>
+      <c r="O68" s="7" t="n">
+        <v>-0.665941</v>
+      </c>
+      <c r="P68" s="7" t="n">
+        <v>7.237902</v>
+      </c>
+      <c r="Q68" s="7" t="n">
+        <v>-0.361363</v>
+      </c>
+      <c r="R68" s="7" t="n">
+        <v>0.158906</v>
+      </c>
+      <c r="S68" s="8" t="n"/>
+      <c r="T68" s="8" t="n"/>
+      <c r="U68" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V68" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W68" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X68" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2896,29 +5701,72 @@
       <c r="B69" s="5" t="n">
         <v>45017</v>
       </c>
-      <c r="C69" s="8" t="n">
+      <c r="C69" s="10" t="n">
+        <v>128.363</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>-0.020251</v>
+      </c>
+      <c r="E69" s="11" t="n">
         <v>6.252845</v>
       </c>
-      <c r="D69" s="8" t="n">
+      <c r="F69" s="10" t="n">
+        <v>128.206218</v>
+      </c>
+      <c r="G69" s="11" t="n">
+        <v>0.386669</v>
+      </c>
+      <c r="H69" s="11" t="n">
         <v>7.669145</v>
       </c>
-      <c r="E69" s="8" t="n"/>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
+      <c r="I69" s="11" t="n">
+        <v>0.495728</v>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>9.543512</v>
+      </c>
+      <c r="K69" s="11" t="n">
+        <v>0.253757</v>
+      </c>
+      <c r="L69" s="11" t="n">
+        <v>5.464561</v>
+      </c>
+      <c r="M69" s="11" t="n">
+        <v>-1.250257</v>
+      </c>
+      <c r="N69" s="11" t="n">
+        <v>2.121448</v>
+      </c>
+      <c r="O69" s="11" t="n">
+        <v>-0.000448</v>
+      </c>
+      <c r="P69" s="11" t="n">
+        <v>6.12753</v>
+      </c>
+      <c r="Q69" s="11" t="n">
+        <v>-2.298459</v>
+      </c>
+      <c r="R69" s="11" t="n">
+        <v>-1.083766</v>
+      </c>
+      <c r="S69" s="12" t="n"/>
+      <c r="T69" s="12" t="n"/>
+      <c r="U69" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V69" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W69" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X69" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2934,28 +5782,71 @@
         <v>45047</v>
       </c>
       <c r="C70" s="6" t="n">
+        <v>128.084</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>-0.217352</v>
+      </c>
+      <c r="E70" s="7" t="n">
         <v>5.835303</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="F70" s="6" t="n">
+        <v>128.62113</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>0.323628</v>
+      </c>
+      <c r="H70" s="7" t="n">
         <v>7.386496</v>
       </c>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I70" s="7" t="n">
+        <v>0.348739</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>9.043877</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>0.292952</v>
+      </c>
+      <c r="L70" s="7" t="n">
+        <v>5.427789</v>
+      </c>
+      <c r="M70" s="7" t="n">
+        <v>-1.881771</v>
+      </c>
+      <c r="N70" s="7" t="n">
+        <v>1.237252</v>
+      </c>
+      <c r="O70" s="7" t="n">
+        <v>-0.340045</v>
+      </c>
+      <c r="P70" s="7" t="n">
+        <v>4.952068</v>
+      </c>
+      <c r="Q70" s="7" t="n">
+        <v>-3.205212</v>
+      </c>
+      <c r="R70" s="7" t="n">
+        <v>-1.833714</v>
+      </c>
+      <c r="S70" s="8" t="n"/>
+      <c r="T70" s="8" t="n"/>
+      <c r="U70" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V70" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W70" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X70" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -2970,29 +5861,72 @@
       <c r="B71" s="5" t="n">
         <v>45078</v>
       </c>
-      <c r="C71" s="8" t="n">
+      <c r="C71" s="10" t="n">
+        <v>128.214</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>0.101496</v>
+      </c>
+      <c r="E71" s="11" t="n">
         <v>5.055554</v>
       </c>
-      <c r="D71" s="8" t="n">
+      <c r="F71" s="10" t="n">
+        <v>129.007619</v>
+      </c>
+      <c r="G71" s="11" t="n">
+        <v>0.300486</v>
+      </c>
+      <c r="H71" s="11" t="n">
         <v>6.886075</v>
       </c>
-      <c r="E71" s="8" t="n"/>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="I71" s="11" t="n">
+        <v>0.279668</v>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>8.264298</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>0.325933</v>
+      </c>
+      <c r="L71" s="11" t="n">
+        <v>5.249086</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>-0.523736</v>
+      </c>
+      <c r="N71" s="11" t="n">
+        <v>-0.355797</v>
+      </c>
+      <c r="O71" s="11" t="n">
+        <v>-0.237693</v>
+      </c>
+      <c r="P71" s="11" t="n">
+        <v>2.89355</v>
+      </c>
+      <c r="Q71" s="11" t="n">
+        <v>-0.776549</v>
+      </c>
+      <c r="R71" s="11" t="n">
+        <v>-3.075736</v>
+      </c>
+      <c r="S71" s="12" t="n"/>
+      <c r="T71" s="12" t="n"/>
+      <c r="U71" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V71" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W71" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X71" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3008,28 +5942,71 @@
         <v>45108</v>
       </c>
       <c r="C72" s="6" t="n">
+        <v>128.832</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>0.482007</v>
+      </c>
+      <c r="E72" s="7" t="n">
         <v>4.785763</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="F72" s="6" t="n">
+        <v>129.511404</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>0.390508</v>
+      </c>
+      <c r="H72" s="7" t="n">
         <v>6.639979</v>
       </c>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I72" s="7" t="n">
+        <v>0.309344</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>7.820211</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>0.489673</v>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>5.235094</v>
+      </c>
+      <c r="M72" s="7" t="n">
+        <v>0.772725</v>
+      </c>
+      <c r="N72" s="7" t="n">
+        <v>-0.668726</v>
+      </c>
+      <c r="O72" s="7" t="n">
+        <v>1.903885</v>
+      </c>
+      <c r="P72" s="7" t="n">
+        <v>3.158614</v>
+      </c>
+      <c r="Q72" s="7" t="n">
+        <v>-0.232452</v>
+      </c>
+      <c r="R72" s="7" t="n">
+        <v>-3.904763</v>
+      </c>
+      <c r="S72" s="8" t="n"/>
+      <c r="T72" s="8" t="n"/>
+      <c r="U72" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V72" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W72" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X72" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3044,29 +6021,72 @@
       <c r="B73" s="5" t="n">
         <v>45139</v>
       </c>
-      <c r="C73" s="8" t="n">
+      <c r="C73" s="10" t="n">
+        <v>129.545</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>0.553434</v>
+      </c>
+      <c r="E73" s="11" t="n">
         <v>4.638014</v>
       </c>
-      <c r="D73" s="8" t="n">
+      <c r="F73" s="10" t="n">
+        <v>129.863773</v>
+      </c>
+      <c r="G73" s="11" t="n">
+        <v>0.272076</v>
+      </c>
+      <c r="H73" s="11" t="n">
         <v>6.082865</v>
       </c>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
+      <c r="I73" s="11" t="n">
+        <v>0.239762</v>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>6.862112</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>0.311484</v>
+      </c>
+      <c r="L73" s="11" t="n">
+        <v>5.148415</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>1.441917</v>
+      </c>
+      <c r="N73" s="11" t="n">
+        <v>0.372755</v>
+      </c>
+      <c r="O73" s="11" t="n">
+        <v>1.740614</v>
+      </c>
+      <c r="P73" s="11" t="n">
+        <v>3.940273</v>
+      </c>
+      <c r="Q73" s="11" t="n">
+        <v>1.170804</v>
+      </c>
+      <c r="R73" s="11" t="n">
+        <v>-2.676264</v>
+      </c>
+      <c r="S73" s="12" t="n"/>
+      <c r="T73" s="12" t="n"/>
+      <c r="U73" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V73" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W73" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X73" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3082,28 +6102,71 @@
         <v>45170</v>
       </c>
       <c r="C74" s="6" t="n">
+        <v>130.12</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>0.443861</v>
+      </c>
+      <c r="E74" s="7" t="n">
         <v>4.454488</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="F74" s="6" t="n">
+        <v>130.333655</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>0.361827</v>
+      </c>
+      <c r="H74" s="7" t="n">
         <v>5.756676</v>
       </c>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I74" s="7" t="n">
+        <v>0.307531</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>6.196741</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>0.427999</v>
+      </c>
+      <c r="L74" s="7" t="n">
+        <v>5.225902</v>
+      </c>
+      <c r="M74" s="7" t="n">
+        <v>0.698333</v>
+      </c>
+      <c r="N74" s="7" t="n">
+        <v>0.598457</v>
+      </c>
+      <c r="O74" s="7" t="n">
+        <v>0.835827</v>
+      </c>
+      <c r="P74" s="7" t="n">
+        <v>3.248031</v>
+      </c>
+      <c r="Q74" s="7" t="n">
+        <v>0.572833</v>
+      </c>
+      <c r="R74" s="7" t="n">
+        <v>-1.709872</v>
+      </c>
+      <c r="S74" s="8" t="n"/>
+      <c r="T74" s="8" t="n"/>
+      <c r="U74" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V74" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W74" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X74" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3118,29 +6181,72 @@
       <c r="B75" s="5" t="n">
         <v>45200</v>
       </c>
-      <c r="C75" s="8" t="n">
+      <c r="C75" s="10" t="n">
+        <v>130.609</v>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>0.375807</v>
+      </c>
+      <c r="E75" s="11" t="n">
         <v>4.257001</v>
       </c>
-      <c r="D75" s="8" t="n">
+      <c r="F75" s="10" t="n">
+        <v>130.836771</v>
+      </c>
+      <c r="G75" s="11" t="n">
+        <v>0.386021</v>
+      </c>
+      <c r="H75" s="11" t="n">
         <v>5.502278</v>
       </c>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="I75" s="11" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>5.635204</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0.440362</v>
+      </c>
+      <c r="L75" s="11" t="n">
+        <v>5.341082</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0.344449</v>
+      </c>
+      <c r="N75" s="11" t="n">
+        <v>0.561435</v>
+      </c>
+      <c r="O75" s="11" t="n">
+        <v>-2.086801</v>
+      </c>
+      <c r="P75" s="11" t="n">
+        <v>1.621882</v>
+      </c>
+      <c r="Q75" s="11" t="n">
+        <v>2.569413</v>
+      </c>
+      <c r="R75" s="11" t="n">
+        <v>-0.347031</v>
+      </c>
+      <c r="S75" s="12" t="n"/>
+      <c r="T75" s="12" t="n"/>
+      <c r="U75" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V75" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W75" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X75" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3156,28 +6262,71 @@
         <v>45231</v>
       </c>
       <c r="C76" s="6" t="n">
+        <v>131.445</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>0.640078</v>
+      </c>
+      <c r="E76" s="7" t="n">
         <v>4.323912</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="F76" s="6" t="n">
+        <v>131.182524</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>0.264263</v>
+      </c>
+      <c r="H76" s="7" t="n">
         <v>5.30488</v>
       </c>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="I76" s="7" t="n">
+        <v>0.138738</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>5.327552</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>0.416909</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>5.2774</v>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>1.810064</v>
+      </c>
+      <c r="N76" s="7" t="n">
+        <v>1.426385</v>
+      </c>
+      <c r="O76" s="7" t="n">
+        <v>0.786852</v>
+      </c>
+      <c r="P76" s="7" t="n">
+        <v>2.85078</v>
+      </c>
+      <c r="Q76" s="7" t="n">
+        <v>2.70395</v>
+      </c>
+      <c r="R76" s="7" t="n">
+        <v>0.236292</v>
+      </c>
+      <c r="S76" s="8" t="n"/>
+      <c r="T76" s="8" t="n"/>
+      <c r="U76" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V76" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W76" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X76" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3192,29 +6341,72 @@
       <c r="B77" s="5" t="n">
         <v>45261</v>
       </c>
-      <c r="C77" s="8" t="n">
+      <c r="C77" s="10" t="n">
+        <v>132.373</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>0.705999</v>
+      </c>
+      <c r="E77" s="11" t="n">
         <v>4.66089</v>
       </c>
-      <c r="D77" s="8" t="n">
+      <c r="F77" s="10" t="n">
+        <v>131.757779</v>
+      </c>
+      <c r="G77" s="11" t="n">
+        <v>0.438515</v>
+      </c>
+      <c r="H77" s="11" t="n">
         <v>5.087704</v>
       </c>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
+      <c r="I77" s="11" t="n">
+        <v>0.320026</v>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>4.88757</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>0.582205</v>
+      </c>
+      <c r="L77" s="11" t="n">
+        <v>5.330793</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>1.525356</v>
+      </c>
+      <c r="N77" s="11" t="n">
+        <v>3.387073</v>
+      </c>
+      <c r="O77" s="11" t="n">
+        <v>3.247726</v>
+      </c>
+      <c r="P77" s="11" t="n">
+        <v>5.661403</v>
+      </c>
+      <c r="Q77" s="11" t="n">
+        <v>0.048766</v>
+      </c>
+      <c r="R77" s="11" t="n">
+        <v>1.455047</v>
+      </c>
+      <c r="S77" s="12" t="n"/>
+      <c r="T77" s="12" t="n"/>
+      <c r="U77" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V77" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W77" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X77" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3230,28 +6422,71 @@
         <v>45292</v>
       </c>
       <c r="C78" s="6" t="n">
+        <v>133.555</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>0.892931</v>
+      </c>
+      <c r="E78" s="7" t="n">
         <v>4.883929</v>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="F78" s="6" t="n">
+        <v>132.291221</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>0.404866</v>
+      </c>
+      <c r="H78" s="7" t="n">
         <v>4.76431</v>
       </c>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="I78" s="7" t="n">
+        <v>0.405908</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>4.367089</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>0.403605</v>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>5.248829</v>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>2.374536</v>
+      </c>
+      <c r="N78" s="7" t="n">
+        <v>5.241315</v>
+      </c>
+      <c r="O78" s="7" t="n">
+        <v>4.401886</v>
+      </c>
+      <c r="P78" s="7" t="n">
+        <v>9.752554</v>
+      </c>
+      <c r="Q78" s="7" t="n">
+        <v>0.580914</v>
+      </c>
+      <c r="R78" s="7" t="n">
+        <v>1.413322</v>
+      </c>
+      <c r="S78" s="8" t="n"/>
+      <c r="T78" s="8" t="n"/>
+      <c r="U78" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V78" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W78" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X78" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3266,29 +6501,72 @@
       <c r="B79" s="5" t="n">
         <v>45323</v>
       </c>
-      <c r="C79" s="8" t="n">
+      <c r="C79" s="10" t="n">
+        <v>133.681</v>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>0.094343</v>
+      </c>
+      <c r="E79" s="11" t="n">
         <v>4.400762</v>
       </c>
-      <c r="D79" s="8" t="n">
+      <c r="F79" s="10" t="n">
+        <v>132.945408</v>
+      </c>
+      <c r="G79" s="11" t="n">
+        <v>0.494505</v>
+      </c>
+      <c r="H79" s="11" t="n">
         <v>4.643099</v>
       </c>
-      <c r="E79" s="8" t="n"/>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
+      <c r="I79" s="11" t="n">
+        <v>0.401134</v>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>4.108937</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>0.607443</v>
+      </c>
+      <c r="L79" s="11" t="n">
+        <v>5.295219</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>-1.096859</v>
+      </c>
+      <c r="N79" s="11" t="n">
+        <v>3.673864</v>
+      </c>
+      <c r="O79" s="11" t="n">
+        <v>-4.603234</v>
+      </c>
+      <c r="P79" s="11" t="n">
+        <v>4.773386</v>
+      </c>
+      <c r="Q79" s="11" t="n">
+        <v>2.123122</v>
+      </c>
+      <c r="R79" s="11" t="n">
+        <v>2.748879</v>
+      </c>
+      <c r="S79" s="12" t="n"/>
+      <c r="T79" s="12" t="n"/>
+      <c r="U79" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V79" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W79" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X79" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3304,28 +6582,71 @@
         <v>45352</v>
       </c>
       <c r="C80" s="6" t="n">
+        <v>134.065</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>0.287251</v>
+      </c>
+      <c r="E80" s="7" t="n">
         <v>4.420939</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="F80" s="6" t="n">
+        <v>133.524017</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>0.435223</v>
+      </c>
+      <c r="H80" s="7" t="n">
         <v>4.550556</v>
       </c>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I80" s="7" t="n">
+        <v>0.224167</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>3.878943</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>0.689984</v>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>5.369066</v>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>-0.158863</v>
+      </c>
+      <c r="N80" s="7" t="n">
+        <v>4.029858</v>
+      </c>
+      <c r="O80" s="7" t="n">
+        <v>-0.529523</v>
+      </c>
+      <c r="P80" s="7" t="n">
+        <v>4.917275</v>
+      </c>
+      <c r="Q80" s="7" t="n">
+        <v>0.159103</v>
+      </c>
+      <c r="R80" s="7" t="n">
+        <v>3.285591</v>
+      </c>
+      <c r="S80" s="8" t="n"/>
+      <c r="T80" s="8" t="n"/>
+      <c r="U80" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V80" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W80" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X80" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3340,29 +6661,72 @@
       <c r="B81" s="5" t="n">
         <v>45383</v>
       </c>
-      <c r="C81" s="8" t="n">
+      <c r="C81" s="10" t="n">
+        <v>134.336</v>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>0.202141</v>
+      </c>
+      <c r="E81" s="11" t="n">
         <v>4.65321</v>
       </c>
-      <c r="D81" s="8" t="n">
+      <c r="F81" s="10" t="n">
+        <v>133.803032</v>
+      </c>
+      <c r="G81" s="11" t="n">
+        <v>0.208962</v>
+      </c>
+      <c r="H81" s="11" t="n">
         <v>4.365478</v>
       </c>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
+      <c r="I81" s="11" t="n">
+        <v>0.295778</v>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>3.672261</v>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>0.104654</v>
+      </c>
+      <c r="L81" s="11" t="n">
+        <v>5.212356</v>
+      </c>
+      <c r="M81" s="11" t="n">
+        <v>0.180515</v>
+      </c>
+      <c r="N81" s="11" t="n">
+        <v>5.537133</v>
+      </c>
+      <c r="O81" s="11" t="n">
+        <v>2.320763</v>
+      </c>
+      <c r="P81" s="11" t="n">
+        <v>7.352637</v>
+      </c>
+      <c r="Q81" s="11" t="n">
+        <v>-1.642846</v>
+      </c>
+      <c r="R81" s="11" t="n">
+        <v>3.978675</v>
+      </c>
+      <c r="S81" s="12" t="n"/>
+      <c r="T81" s="12" t="n"/>
+      <c r="U81" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V81" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W81" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X81" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3378,28 +6742,71 @@
         <v>45413</v>
       </c>
       <c r="C82" s="6" t="n">
+        <v>134.087</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>-0.185356</v>
+      </c>
+      <c r="E82" s="7" t="n">
         <v>4.686768</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="F82" s="6" t="n">
+        <v>134.035347</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>0.173624</v>
+      </c>
+      <c r="H82" s="7" t="n">
         <v>4.20943</v>
       </c>
-      <c r="E82" s="6" t="n"/>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I82" s="7" t="n">
+        <v>0.06972399999999999</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>3.384006</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>0.298697</v>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>5.218383</v>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>-1.277352</v>
+      </c>
+      <c r="N82" s="7" t="n">
+        <v>6.187253</v>
+      </c>
+      <c r="O82" s="7" t="n">
+        <v>0.666879</v>
+      </c>
+      <c r="P82" s="7" t="n">
+        <v>8.437284999999999</v>
+      </c>
+      <c r="Q82" s="7" t="n">
+        <v>-3.000467</v>
+      </c>
+      <c r="R82" s="7" t="n">
+        <v>4.198617</v>
+      </c>
+      <c r="S82" s="8" t="n"/>
+      <c r="T82" s="8" t="n"/>
+      <c r="U82" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V82" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W82" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X82" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3414,29 +6821,72 @@
       <c r="B83" s="5" t="n">
         <v>45444</v>
       </c>
-      <c r="C83" s="8" t="n">
+      <c r="C83" s="10" t="n">
+        <v>134.594</v>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>0.378113</v>
+      </c>
+      <c r="E83" s="11" t="n">
         <v>4.976056</v>
       </c>
-      <c r="D83" s="8" t="n">
+      <c r="F83" s="10" t="n">
+        <v>134.329313</v>
+      </c>
+      <c r="G83" s="11" t="n">
+        <v>0.21932</v>
+      </c>
+      <c r="H83" s="11" t="n">
         <v>4.125101</v>
       </c>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
+      <c r="I83" s="11" t="n">
+        <v>0.181215</v>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>3.282505</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>0.265086</v>
+      </c>
+      <c r="L83" s="11" t="n">
+        <v>5.154569</v>
+      </c>
+      <c r="M83" s="11" t="n">
+        <v>0.8686</v>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>7.67352</v>
+      </c>
+      <c r="O83" s="11" t="n">
+        <v>1.535227</v>
+      </c>
+      <c r="P83" s="11" t="n">
+        <v>10.364371</v>
+      </c>
+      <c r="Q83" s="11" t="n">
+        <v>0.255451</v>
+      </c>
+      <c r="R83" s="11" t="n">
+        <v>5.282362</v>
+      </c>
+      <c r="S83" s="12" t="n"/>
+      <c r="T83" s="12" t="n"/>
+      <c r="U83" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V83" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W83" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X83" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3452,28 +6902,71 @@
         <v>45474</v>
       </c>
       <c r="C84" s="6" t="n">
+        <v>136.003</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1.046852</v>
+      </c>
+      <c r="E84" s="7" t="n">
         <v>5.566164</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="F84" s="6" t="n">
+        <v>134.753022</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>0.315425</v>
+      </c>
+      <c r="H84" s="7" t="n">
         <v>4.047225</v>
       </c>
-      <c r="E84" s="6" t="n"/>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I84" s="7" t="inlineStr">
+      <c r="I84" s="7" t="n">
+        <v>0.11896</v>
+      </c>
+      <c r="J84" s="7" t="n">
+        <v>3.086478</v>
+      </c>
+      <c r="K84" s="7" t="n">
+        <v>0.551189</v>
+      </c>
+      <c r="L84" s="7" t="n">
+        <v>5.21894</v>
+      </c>
+      <c r="M84" s="7" t="n">
+        <v>3.288795</v>
+      </c>
+      <c r="N84" s="7" t="n">
+        <v>10.361888</v>
+      </c>
+      <c r="O84" s="7" t="n">
+        <v>5.002818</v>
+      </c>
+      <c r="P84" s="7" t="n">
+        <v>13.72059</v>
+      </c>
+      <c r="Q84" s="7" t="n">
+        <v>1.69215</v>
+      </c>
+      <c r="R84" s="7" t="n">
+        <v>7.31335</v>
+      </c>
+      <c r="S84" s="8" t="n"/>
+      <c r="T84" s="8" t="n"/>
+      <c r="U84" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V84" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W84" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X84" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3488,29 +6981,72 @@
       <c r="B85" s="5" t="n">
         <v>45505</v>
       </c>
-      <c r="C85" s="8" t="n">
+      <c r="C85" s="10" t="n">
+        <v>136.013</v>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>0.007353</v>
+      </c>
+      <c r="E85" s="11" t="n">
         <v>4.99286</v>
       </c>
-      <c r="D85" s="8" t="n">
+      <c r="F85" s="10" t="n">
+        <v>135.053143</v>
+      </c>
+      <c r="G85" s="11" t="n">
+        <v>0.22272</v>
+      </c>
+      <c r="H85" s="11" t="n">
         <v>3.996011</v>
       </c>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
+      <c r="I85" s="11" t="n">
+        <v>0.175758</v>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>3.020656</v>
+      </c>
+      <c r="K85" s="11" t="n">
+        <v>0.274818</v>
+      </c>
+      <c r="L85" s="11" t="n">
+        <v>5.18048</v>
+      </c>
+      <c r="M85" s="11" t="n">
+        <v>-0.700589</v>
+      </c>
+      <c r="N85" s="11" t="n">
+        <v>8.030988000000001</v>
+      </c>
+      <c r="O85" s="11" t="n">
+        <v>-2.079737</v>
+      </c>
+      <c r="P85" s="11" t="n">
+        <v>9.450392000000001</v>
+      </c>
+      <c r="Q85" s="11" t="n">
+        <v>0.475565</v>
+      </c>
+      <c r="R85" s="11" t="n">
+        <v>6.5759</v>
+      </c>
+      <c r="S85" s="12" t="n"/>
+      <c r="T85" s="12" t="n"/>
+      <c r="U85" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V85" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W85" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X85" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3526,28 +7062,71 @@
         <v>45536</v>
       </c>
       <c r="C86" s="6" t="n">
+        <v>136.08</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>0.04926</v>
+      </c>
+      <c r="E86" s="7" t="n">
         <v>4.580387</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="F86" s="6" t="n">
+        <v>135.433359</v>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>0.28153</v>
+      </c>
+      <c r="H86" s="7" t="n">
         <v>3.912806</v>
       </c>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="I86" s="7" t="n">
+        <v>0.205739</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>2.916111</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>0.354062</v>
+      </c>
+      <c r="L86" s="7" t="n">
+        <v>5.103044</v>
+      </c>
+      <c r="M86" s="7" t="n">
+        <v>-0.724924</v>
+      </c>
+      <c r="N86" s="7" t="n">
+        <v>6.504091</v>
+      </c>
+      <c r="O86" s="7" t="n">
+        <v>-1.645005</v>
+      </c>
+      <c r="P86" s="7" t="n">
+        <v>6.757618</v>
+      </c>
+      <c r="Q86" s="7" t="n">
+        <v>0.034536</v>
+      </c>
+      <c r="R86" s="7" t="n">
+        <v>6.005473</v>
+      </c>
+      <c r="S86" s="8" t="n"/>
+      <c r="T86" s="8" t="n"/>
+      <c r="U86" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V86" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W86" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X86" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3562,29 +7141,72 @@
       <c r="B87" s="5" t="n">
         <v>45566</v>
       </c>
-      <c r="C87" s="8" t="n">
+      <c r="C87" s="10" t="n">
+        <v>136.828</v>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>0.549677</v>
+      </c>
+      <c r="E87" s="11" t="n">
         <v>4.76154</v>
       </c>
-      <c r="D87" s="8" t="n">
+      <c r="F87" s="10" t="n">
+        <v>135.812502</v>
+      </c>
+      <c r="G87" s="11" t="n">
+        <v>0.279949</v>
+      </c>
+      <c r="H87" s="11" t="n">
         <v>3.803007</v>
       </c>
-      <c r="E87" s="8" t="n"/>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
+      <c r="I87" s="11" t="n">
+        <v>0.239895</v>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>2.812023</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>0.318223</v>
+      </c>
+      <c r="L87" s="11" t="n">
+        <v>4.975235</v>
+      </c>
+      <c r="M87" s="11" t="n">
+        <v>1.455336</v>
+      </c>
+      <c r="N87" s="11" t="n">
+        <v>7.68317</v>
+      </c>
+      <c r="O87" s="11" t="n">
+        <v>1.732067</v>
+      </c>
+      <c r="P87" s="11" t="n">
+        <v>10.921441</v>
+      </c>
+      <c r="Q87" s="11" t="n">
+        <v>1.230749</v>
+      </c>
+      <c r="R87" s="11" t="n">
+        <v>4.621964</v>
+      </c>
+      <c r="S87" s="12" t="n"/>
+      <c r="T87" s="12" t="n"/>
+      <c r="U87" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V87" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W87" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X87" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3600,28 +7222,71 @@
         <v>45597</v>
       </c>
       <c r="C88" s="6" t="n">
+        <v>137.424</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>0.435583</v>
+      </c>
+      <c r="E88" s="7" t="n">
         <v>4.548671</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="F88" s="6" t="n">
+        <v>135.875585</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>0.046448</v>
+      </c>
+      <c r="H88" s="7" t="n">
         <v>3.577505</v>
       </c>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I88" s="7" t="n">
+        <v>-0.270194</v>
+      </c>
+      <c r="J88" s="7" t="n">
+        <v>2.392174</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>0.348787</v>
+      </c>
+      <c r="L88" s="7" t="n">
+        <v>4.904021</v>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>1.731273</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>7.599834</v>
+      </c>
+      <c r="O88" s="7" t="n">
+        <v>0.62265</v>
+      </c>
+      <c r="P88" s="7" t="n">
+        <v>10.740728</v>
+      </c>
+      <c r="Q88" s="7" t="n">
+        <v>2.635454</v>
+      </c>
+      <c r="R88" s="7" t="n">
+        <v>4.552189</v>
+      </c>
+      <c r="S88" s="8" t="n"/>
+      <c r="T88" s="8" t="n"/>
+      <c r="U88" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V88" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W88" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X88" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3636,29 +7301,72 @@
       <c r="B89" s="5" t="n">
         <v>45627</v>
       </c>
-      <c r="C89" s="8" t="n">
+      <c r="C89" s="10" t="n">
+        <v>137.949</v>
+      </c>
+      <c r="D89" s="11" t="n">
+        <v>0.382029</v>
+      </c>
+      <c r="E89" s="11" t="n">
         <v>4.212339</v>
       </c>
-      <c r="D89" s="8" t="n">
+      <c r="F89" s="10" t="n">
+        <v>136.567452</v>
+      </c>
+      <c r="G89" s="11" t="n">
+        <v>0.509192</v>
+      </c>
+      <c r="H89" s="11" t="n">
         <v>3.65039</v>
       </c>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
+      <c r="I89" s="11" t="n">
+        <v>0.400635</v>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>2.474449</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>0.612205</v>
+      </c>
+      <c r="L89" s="11" t="n">
+        <v>4.93531</v>
+      </c>
+      <c r="M89" s="11" t="n">
+        <v>-0.035421</v>
+      </c>
+      <c r="N89" s="11" t="n">
+        <v>5.945673</v>
+      </c>
+      <c r="O89" s="11" t="n">
+        <v>-0.640364</v>
+      </c>
+      <c r="P89" s="11" t="n">
+        <v>6.570467</v>
+      </c>
+      <c r="Q89" s="11" t="n">
+        <v>0.448288</v>
+      </c>
+      <c r="R89" s="11" t="n">
+        <v>4.969694</v>
+      </c>
+      <c r="S89" s="12" t="n"/>
+      <c r="T89" s="12" t="n"/>
+      <c r="U89" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V89" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W89" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X89" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3674,28 +7382,71 @@
         <v>45658</v>
       </c>
       <c r="C90" s="6" t="n">
+        <v>138.343</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>0.285613</v>
+      </c>
+      <c r="E90" s="7" t="n">
         <v>3.58504</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="F90" s="6" t="n">
+        <v>137.134007</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>0.414853</v>
+      </c>
+      <c r="H90" s="7" t="n">
         <v>3.660701</v>
       </c>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="inlineStr">
+      <c r="I90" s="7" t="n">
+        <v>0.670005</v>
+      </c>
+      <c r="J90" s="7" t="n">
+        <v>2.743986</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>0.17324</v>
+      </c>
+      <c r="L90" s="7" t="n">
+        <v>4.694547</v>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>-0.138767</v>
+      </c>
+      <c r="N90" s="7" t="n">
+        <v>3.344698</v>
+      </c>
+      <c r="O90" s="7" t="n">
+        <v>-1.491108</v>
+      </c>
+      <c r="P90" s="7" t="n">
+        <v>0.555067</v>
+      </c>
+      <c r="Q90" s="7" t="n">
+        <v>0.9308380000000001</v>
+      </c>
+      <c r="R90" s="7" t="n">
+        <v>5.334886</v>
+      </c>
+      <c r="S90" s="8" t="n"/>
+      <c r="T90" s="8" t="n"/>
+      <c r="U90" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V90" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W90" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X90" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3710,29 +7461,72 @@
       <c r="B91" s="5" t="n">
         <v>45689</v>
       </c>
-      <c r="C91" s="8" t="n">
+      <c r="C91" s="10" t="n">
+        <v>138.726</v>
+      </c>
+      <c r="D91" s="11" t="n">
+        <v>0.276848</v>
+      </c>
+      <c r="E91" s="11" t="n">
         <v>3.77391</v>
       </c>
-      <c r="D91" s="8" t="n">
+      <c r="F91" s="10" t="n">
+        <v>137.792658</v>
+      </c>
+      <c r="G91" s="11" t="n">
+        <v>0.480298</v>
+      </c>
+      <c r="H91" s="11" t="n">
         <v>3.646045</v>
       </c>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
+      <c r="I91" s="11" t="n">
+        <v>0.406287</v>
+      </c>
+      <c r="J91" s="11" t="n">
+        <v>2.74926</v>
+      </c>
+      <c r="K91" s="11" t="n">
+        <v>0.550729</v>
+      </c>
+      <c r="L91" s="11" t="n">
+        <v>4.635529</v>
+      </c>
+      <c r="M91" s="11" t="n">
+        <v>-0.394453</v>
+      </c>
+      <c r="N91" s="11" t="n">
+        <v>4.078647</v>
+      </c>
+      <c r="O91" s="11" t="n">
+        <v>-1.440405</v>
+      </c>
+      <c r="P91" s="11" t="n">
+        <v>3.888917</v>
+      </c>
+      <c r="Q91" s="11" t="n">
+        <v>0.412968</v>
+      </c>
+      <c r="R91" s="11" t="n">
+        <v>3.570948</v>
+      </c>
+      <c r="S91" s="12" t="n"/>
+      <c r="T91" s="12" t="n"/>
+      <c r="U91" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V91" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W91" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X91" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3748,28 +7542,71 @@
         <v>45717</v>
       </c>
       <c r="C92" s="6" t="n">
+        <v>139.161</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>0.313568</v>
+      </c>
+      <c r="E92" s="7" t="n">
         <v>3.801141</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="F92" s="6" t="n">
+        <v>138.386099</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>0.430677</v>
+      </c>
+      <c r="H92" s="7" t="n">
         <v>3.641353</v>
       </c>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="I92" s="7" t="n">
+        <v>0.447925</v>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>2.978655</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>0.414287</v>
+      </c>
+      <c r="L92" s="7" t="n">
+        <v>4.349029</v>
+      </c>
+      <c r="M92" s="7" t="n">
+        <v>-0.078703</v>
+      </c>
+      <c r="N92" s="7" t="n">
+        <v>4.162209</v>
+      </c>
+      <c r="O92" s="7" t="n">
+        <v>0.411968</v>
+      </c>
+      <c r="P92" s="7" t="n">
+        <v>4.872229</v>
+      </c>
+      <c r="Q92" s="7" t="n">
+        <v>-0.450485</v>
+      </c>
+      <c r="R92" s="7" t="n">
+        <v>2.940596</v>
+      </c>
+      <c r="S92" s="8" t="n"/>
+      <c r="T92" s="8" t="n"/>
+      <c r="U92" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V92" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W92" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X92" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3784,29 +7621,72 @@
       <c r="B93" s="5" t="n">
         <v>45748</v>
       </c>
-      <c r="C93" s="8" t="n">
+      <c r="C93" s="10" t="n">
+        <v>139.62</v>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>0.329834</v>
+      </c>
+      <c r="E93" s="11" t="n">
         <v>3.933421</v>
       </c>
-      <c r="D93" s="8" t="n">
+      <c r="F93" s="10" t="n">
+        <v>139.065495</v>
+      </c>
+      <c r="G93" s="11" t="n">
+        <v>0.490942</v>
+      </c>
+      <c r="H93" s="11" t="n">
         <v>3.932992</v>
       </c>
-      <c r="E93" s="8" t="n"/>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
+      <c r="I93" s="11" t="n">
+        <v>0.688053</v>
+      </c>
+      <c r="J93" s="11" t="n">
+        <v>3.381424</v>
+      </c>
+      <c r="K93" s="11" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="L93" s="11" t="n">
+        <v>4.556379</v>
+      </c>
+      <c r="M93" s="11" t="n">
+        <v>-0.209482</v>
+      </c>
+      <c r="N93" s="11" t="n">
+        <v>3.756712</v>
+      </c>
+      <c r="O93" s="11" t="n">
+        <v>1.600084</v>
+      </c>
+      <c r="P93" s="11" t="n">
+        <v>4.133579</v>
+      </c>
+      <c r="Q93" s="11" t="n">
+        <v>-1.59247</v>
+      </c>
+      <c r="R93" s="11" t="n">
+        <v>2.993318</v>
+      </c>
+      <c r="S93" s="12" t="n"/>
+      <c r="T93" s="12" t="n"/>
+      <c r="U93" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V93" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W93" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X93" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3822,28 +7702,71 @@
         <v>45778</v>
       </c>
       <c r="C94" s="6" t="n">
+        <v>140.012</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>0.280762</v>
+      </c>
+      <c r="E94" s="7" t="n">
         <v>4.418773</v>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="F94" s="6" t="n">
+        <v>139.476052</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>0.295226</v>
+      </c>
+      <c r="H94" s="7" t="n">
         <v>4.059157</v>
       </c>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I94" s="7" t="n">
+        <v>0.353782</v>
+      </c>
+      <c r="J94" s="7" t="n">
+        <v>3.674881</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>0.23935</v>
+      </c>
+      <c r="L94" s="7" t="n">
+        <v>4.494512</v>
+      </c>
+      <c r="M94" s="7" t="n">
+        <v>0.231761</v>
+      </c>
+      <c r="N94" s="7" t="n">
+        <v>5.342778</v>
+      </c>
+      <c r="O94" s="7" t="n">
+        <v>3.207639</v>
+      </c>
+      <c r="P94" s="7" t="n">
+        <v>6.761836</v>
+      </c>
+      <c r="Q94" s="7" t="n">
+        <v>-2.116385</v>
+      </c>
+      <c r="R94" s="7" t="n">
+        <v>3.93203</v>
+      </c>
+      <c r="S94" s="8" t="n"/>
+      <c r="T94" s="8" t="n"/>
+      <c r="U94" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V94" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W94" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X94" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3858,31 +7781,72 @@
       <c r="B95" s="5" t="n">
         <v>45809</v>
       </c>
-      <c r="C95" s="8" t="n">
+      <c r="C95" s="10" t="n">
+        <v>140.405</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="E95" s="11" t="n">
         <v>4.317429</v>
       </c>
-      <c r="D95" s="8" t="n">
+      <c r="F95" s="10" t="n">
+        <v>140.02556</v>
+      </c>
+      <c r="G95" s="11" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="H95" s="11" t="n">
         <v>4.240509</v>
       </c>
-      <c r="E95" s="8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
+      <c r="I95" s="11" t="n">
+        <v>0.406717</v>
+      </c>
+      <c r="J95" s="11" t="n">
+        <v>3.908248</v>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>0.381811</v>
+      </c>
+      <c r="L95" s="11" t="n">
+        <v>4.616161</v>
+      </c>
+      <c r="M95" s="11" t="n">
+        <v>-0.100263</v>
+      </c>
+      <c r="N95" s="11" t="n">
+        <v>4.33094</v>
+      </c>
+      <c r="O95" s="11" t="n">
+        <v>-0.09903099999999999</v>
+      </c>
+      <c r="P95" s="11" t="n">
+        <v>5.043453</v>
+      </c>
+      <c r="Q95" s="11" t="n">
+        <v>-0.101288</v>
+      </c>
+      <c r="R95" s="11" t="n">
+        <v>3.562209</v>
+      </c>
+      <c r="S95" s="12" t="n"/>
+      <c r="T95" s="12" t="n"/>
+      <c r="U95" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V95" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W95" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X95" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3898,30 +7862,71 @@
         <v>45839</v>
       </c>
       <c r="C96" s="6" t="n">
+        <v>140.78</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>0.267085</v>
+      </c>
+      <c r="E96" s="7" t="n">
         <v>3.512423</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="F96" s="6" t="n">
+        <v>140.45448</v>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>0.306316</v>
+      </c>
+      <c r="H96" s="7" t="n">
         <v>4.231043</v>
       </c>
-      <c r="E96" s="6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I96" s="7" t="n">
+        <v>0.223921</v>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>4.017181</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="L96" s="7" t="n">
+        <v>4.443306</v>
+      </c>
+      <c r="M96" s="7" t="n">
+        <v>0.133813</v>
+      </c>
+      <c r="N96" s="7" t="n">
+        <v>1.144126</v>
+      </c>
+      <c r="O96" s="7" t="n">
+        <v>0.134267</v>
+      </c>
+      <c r="P96" s="7" t="n">
+        <v>0.173018</v>
+      </c>
+      <c r="Q96" s="7" t="n">
+        <v>0.133436</v>
+      </c>
+      <c r="R96" s="7" t="n">
+        <v>1.974831</v>
+      </c>
+      <c r="S96" s="8" t="n"/>
+      <c r="T96" s="8" t="n"/>
+      <c r="U96" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V96" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W96" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X96" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3936,31 +7941,72 @@
       <c r="B97" s="5" t="n">
         <v>45870</v>
       </c>
-      <c r="C97" s="8" t="n">
+      <c r="C97" s="10" t="n">
+        <v>140.867</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>0.061799</v>
+      </c>
+      <c r="E97" s="11" t="n">
         <v>3.568777</v>
       </c>
-      <c r="D97" s="8" t="n">
+      <c r="F97" s="10" t="n">
+        <v>140.761891</v>
+      </c>
+      <c r="G97" s="11" t="n">
+        <v>0.218869</v>
+      </c>
+      <c r="H97" s="11" t="n">
         <v>4.227038</v>
       </c>
-      <c r="E97" s="8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
+      <c r="I97" s="11" t="n">
+        <v>0.207582</v>
+      </c>
+      <c r="J97" s="11" t="n">
+        <v>4.050225</v>
+      </c>
+      <c r="K97" s="11" t="n">
+        <v>0.229636</v>
+      </c>
+      <c r="L97" s="11" t="n">
+        <v>4.396247</v>
+      </c>
+      <c r="M97" s="11" t="n">
+        <v>-0.473466</v>
+      </c>
+      <c r="N97" s="11" t="n">
+        <v>1.375467</v>
+      </c>
+      <c r="O97" s="11" t="n">
+        <v>-1.066931</v>
+      </c>
+      <c r="P97" s="11" t="n">
+        <v>1.209125</v>
+      </c>
+      <c r="Q97" s="11" t="n">
+        <v>0.020298</v>
+      </c>
+      <c r="R97" s="11" t="n">
+        <v>1.512771</v>
+      </c>
+      <c r="S97" s="12" t="n"/>
+      <c r="T97" s="12" t="n"/>
+      <c r="U97" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V97" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W97" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X97" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -3976,30 +8022,75 @@
         <v>45901</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>3.760288</v>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>4.277929</v>
-      </c>
-      <c r="E98" s="6" t="n">
+        <v>141.197</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>141.227101</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J98" s="7" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L98" s="7" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="M98" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N98" s="7" t="n">
         <v>2.02</v>
       </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="O98" s="7" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="P98" s="7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q98" s="7" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="R98" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S98" s="8" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="T98" s="8" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="U98" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V98" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W98" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X98" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4014,31 +8105,76 @@
       <c r="B99" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="C99" s="8" t="n">
-        <v>3.566521</v>
-      </c>
-      <c r="D99" s="8" t="n">
-        <v>4.28375</v>
-      </c>
-      <c r="E99" s="8" t="n">
+      <c r="C99" s="10" t="n">
+        <v>141.708</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="F99" s="10" t="n">
+        <v>141.630371</v>
+      </c>
+      <c r="G99" s="11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H99" s="11" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I99" s="11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J99" s="11" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="K99" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L99" s="11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="M99" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N99" s="11" t="n">
         <v>1.18</v>
       </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
+      <c r="O99" s="11" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="P99" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q99" s="11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R99" s="11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S99" s="12" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="T99" s="12" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="U99" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V99" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W99" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X99" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4054,30 +8190,75 @@
         <v>45962</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>3.799191</v>
-      </c>
-      <c r="D100" s="6" t="n">
-        <v>4.430588</v>
-      </c>
-      <c r="E100" s="6" t="n">
+        <v>142.645</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>141.895672</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="J100" s="7" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L100" s="7" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="M100" s="7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N100" s="7" t="n">
         <v>1.73</v>
       </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="O100" s="7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P100" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q100" s="7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R100" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S100" s="8" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="T100" s="8" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="U100" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V100" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W100" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X100" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4092,31 +8273,76 @@
       <c r="B101" s="5" t="n">
         <v>45992</v>
       </c>
-      <c r="C101" s="8" t="n">
-        <v>3.691944</v>
-      </c>
-      <c r="D101" s="8" t="n">
-        <v>4.325358</v>
-      </c>
-      <c r="E101" s="8" t="n">
+      <c r="C101" s="10" t="n">
+        <v>143.042</v>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>142.474483</v>
+      </c>
+      <c r="G101" s="11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H101" s="11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I101" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J101" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K101" s="11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L101" s="11" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M101" s="11" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N101" s="11" t="n">
         <v>1.61</v>
       </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
+      <c r="O101" s="11" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="P101" s="11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q101" s="11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R101" s="11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S101" s="12" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="T101" s="12" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="U101" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V101" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W101" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X101" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4132,30 +8358,75 @@
         <v>46023</v>
       </c>
       <c r="C102" s="6" t="n">
-        <v>3.791301</v>
-      </c>
-      <c r="D102" s="6" t="n">
-        <v>4.51917</v>
-      </c>
-      <c r="E102" s="6" t="n">
+        <v>143.588</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>143.331326</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H102" s="7" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J102" s="7" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="K102" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L102" s="7" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="M102" s="7" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="N102" s="7" t="n">
         <v>1.39</v>
       </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H102" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="O102" s="7" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="P102" s="7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q102" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R102" s="7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S102" s="8" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="T102" s="8" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="U102" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V102" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W102" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X102" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4170,31 +8441,76 @@
       <c r="B103" s="5" t="n">
         <v>46054</v>
       </c>
-      <c r="C103" s="8" t="n">
-        <v>4.023038</v>
-      </c>
-      <c r="D103" s="8" t="n">
-        <v>4.497411</v>
-      </c>
-      <c r="E103" s="8" t="n">
+      <c r="C103" s="10" t="n">
+        <v>144.307</v>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F103" s="10" t="n">
+        <v>143.98976</v>
+      </c>
+      <c r="G103" s="11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H103" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I103" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J103" s="11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="K103" s="11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L103" s="11" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="M103" s="11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N103" s="11" t="n">
         <v>2.44</v>
       </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
+      <c r="O103" s="11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P103" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q103" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R103" s="11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S103" s="12" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="T103" s="12" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="U103" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V103" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W103" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X103" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4210,30 +8526,75 @@
         <v>46082</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>4.586774</v>
-      </c>
-      <c r="D104" s="6" t="n">
-        <v>4.449385</v>
-      </c>
-      <c r="E104" s="6" t="n">
+        <v>145.544</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>144.543429</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I104" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J104" s="7" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="K104" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L104" s="7" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M104" s="7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N104" s="7" t="n">
         <v>5.05</v>
       </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="O104" s="7" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="P104" s="7" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="Q104" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R104" s="7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S104" s="8" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="T104" s="8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="U104" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V104" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W104" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X104" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4248,31 +8609,76 @@
       <c r="B105" s="5" t="n">
         <v>46113</v>
       </c>
-      <c r="C105" s="8" t="n">
-        <v>4.448503</v>
-      </c>
-      <c r="D105" s="8" t="n">
-        <v>4.261182</v>
-      </c>
-      <c r="E105" s="8" t="n">
+      <c r="C105" s="10" t="n">
+        <v>145.831</v>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="F105" s="10" t="n">
+        <v>144.991329</v>
+      </c>
+      <c r="G105" s="11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H105" s="11" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="I105" s="11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J105" s="11" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K105" s="11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L105" s="11" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="M105" s="11" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="N105" s="11" t="n">
         <v>5.08</v>
       </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H105" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
+      <c r="O105" s="11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P105" s="11" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="Q105" s="11" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="R105" s="11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S105" s="12" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="T105" s="12" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="U105" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V105" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W105" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X105" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4288,30 +8694,75 @@
         <v>46143</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>3.938948</v>
-      </c>
-      <c r="D106" s="6" t="n">
-        <v>4.186559</v>
-      </c>
-      <c r="E106" s="6" t="n">
+        <v>145.527</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>145.315299</v>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I106" s="7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J106" s="7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L106" s="7" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="M106" s="7" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="N106" s="7" t="n">
         <v>3.1</v>
       </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="O106" s="7" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="P106" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q106" s="7" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="R106" s="7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="S106" s="8" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="T106" s="8" t="n">
+        <v>-0.381</v>
+      </c>
+      <c r="U106" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V106" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W106" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X106" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4326,29 +8777,76 @@
       <c r="B107" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="C107" s="8" t="n">
-        <v>3.365977</v>
-      </c>
-      <c r="D107" s="8" t="n">
-        <v>4.03192</v>
-      </c>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H107" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
+      <c r="C107" s="10" t="n">
+        <v>145.131</v>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="F107" s="10" t="n">
+        <v>145.671279</v>
+      </c>
+      <c r="G107" s="11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H107" s="11" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="I107" s="11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J107" s="11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K107" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L107" s="11" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="M107" s="11" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="N107" s="11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O107" s="11" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="P107" s="11" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="Q107" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="R107" s="11" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="S107" s="12" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="T107" s="12" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="U107" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V107" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W107" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X107" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4364,28 +8862,75 @@
         <v>46204</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>3.11763</v>
-      </c>
-      <c r="D108" s="6" t="n">
-        <v>3.948334</v>
-      </c>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
-        </is>
-      </c>
-      <c r="I108" s="7" t="inlineStr">
+        <v>145.169</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>146.000093</v>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H108" s="7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I108" s="7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J108" s="7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K108" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L108" s="7" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="M108" s="7" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="N108" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O108" s="7" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="P108" s="7" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="Q108" s="7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="R108" s="7" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="S108" s="8" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="T108" s="8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="U108" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V108" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W108" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X108" s="9" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>
@@ -4393,9 +8938,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -8025,19 +8025,19 @@
         <v>141.197</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>0.23</v>
+        <v>0.234264</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>3.76</v>
+        <v>3.760288</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>141.227101</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0.33</v>
+        <v>0.330494</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>4.28</v>
+        <v>4.277929</v>
       </c>
       <c r="I98" s="7" t="n">
         <v>0.34</v>
@@ -8109,19 +8109,19 @@
         <v>141.708</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>0.36</v>
+        <v>0.361906</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>3.57</v>
+        <v>3.566521</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>141.630371</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0.29</v>
+        <v>0.285547</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>4.28</v>
+        <v>4.28375</v>
       </c>
       <c r="I99" s="11" t="n">
         <v>0.17</v>
@@ -8193,19 +8193,19 @@
         <v>142.645</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>0.66</v>
+        <v>0.661219</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>3.8</v>
+        <v>3.799191</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>141.895672</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>0.19</v>
+        <v>0.187319</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>4.43</v>
+        <v>4.430588</v>
       </c>
       <c r="I100" s="7" t="n">
         <v>-0.03</v>
@@ -8277,19 +8277,19 @@
         <v>143.042</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>0.28</v>
+        <v>0.278313</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>3.69</v>
+        <v>3.691944</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>142.474483</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>0.41</v>
+        <v>0.407913</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>4.33</v>
+        <v>4.325358</v>
       </c>
       <c r="I101" s="11" t="n">
         <v>0.33</v>
@@ -8361,19 +8361,19 @@
         <v>143.588</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>0.38</v>
+        <v>0.381706</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>3.79</v>
+        <v>3.791301</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>143.331326</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>0.6</v>
+        <v>0.601401</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>4.52</v>
+        <v>4.51917</v>
       </c>
       <c r="I102" s="7" t="n">
         <v>0.92</v>
@@ -8445,19 +8445,19 @@
         <v>144.307</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>0.5</v>
+        <v>0.500738</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>4.02</v>
+        <v>4.023038</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>143.98976</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>0.46</v>
+        <v>0.459379</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>4.5</v>
+        <v>4.497411</v>
       </c>
       <c r="I103" s="11" t="n">
         <v>0.39</v>
@@ -8529,19 +8529,19 @@
         <v>145.544</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>0.86</v>
+        <v>0.8572</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>4.59</v>
+        <v>4.586774</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>144.543429</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>0.38</v>
+        <v>0.384519</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>4.45</v>
+        <v>4.449385</v>
       </c>
       <c r="I104" s="7" t="n">
         <v>0.29</v>
@@ -8613,19 +8613,19 @@
         <v>145.831</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>0.2</v>
+        <v>0.197191</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>4.45</v>
+        <v>4.448503</v>
       </c>
       <c r="F105" s="10" t="n">
         <v>144.991329</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.31</v>
+        <v>0.309872</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>4.26</v>
+        <v>4.261182</v>
       </c>
       <c r="I105" s="11" t="n">
         <v>0.31</v>
@@ -8697,19 +8697,19 @@
         <v>145.527</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>-0.21</v>
+        <v>-0.20846</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>3.94</v>
+        <v>3.938948</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>145.315299</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.22</v>
+        <v>0.223441</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>4.19</v>
+        <v>4.186559</v>
       </c>
       <c r="I106" s="7" t="n">
         <v>0.16</v>
@@ -8781,19 +8781,19 @@
         <v>145.131</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>-0.27</v>
+        <v>-0.272114</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>3.37</v>
+        <v>3.365977</v>
       </c>
       <c r="F107" s="10" t="n">
         <v>145.671279</v>
       </c>
       <c r="G107" s="11" t="n">
-        <v>0.24</v>
+        <v>0.24497</v>
       </c>
       <c r="H107" s="11" t="n">
-        <v>4.03</v>
+        <v>4.03192</v>
       </c>
       <c r="I107" s="11" t="n">
         <v>0.18</v>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -8025,19 +8025,19 @@
         <v>141.197</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>0.234264</v>
+        <v>0.23</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>3.760288</v>
+        <v>3.76</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>141.227101</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0.330494</v>
+        <v>0.33</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>4.277929</v>
+        <v>4.28</v>
       </c>
       <c r="I98" s="7" t="n">
         <v>0.34</v>
@@ -8109,19 +8109,19 @@
         <v>141.708</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>0.361906</v>
+        <v>0.36</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>3.566521</v>
+        <v>3.57</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>141.630371</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0.285547</v>
+        <v>0.29</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>4.28375</v>
+        <v>4.28</v>
       </c>
       <c r="I99" s="11" t="n">
         <v>0.17</v>
@@ -8193,19 +8193,19 @@
         <v>142.645</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>0.661219</v>
+        <v>0.66</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>3.799191</v>
+        <v>3.8</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>141.895672</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>0.187319</v>
+        <v>0.19</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>4.430588</v>
+        <v>4.43</v>
       </c>
       <c r="I100" s="7" t="n">
         <v>-0.03</v>
@@ -8277,19 +8277,19 @@
         <v>143.042</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>0.278313</v>
+        <v>0.28</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>3.691944</v>
+        <v>3.69</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>142.474483</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>0.407913</v>
+        <v>0.41</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>4.325358</v>
+        <v>4.33</v>
       </c>
       <c r="I101" s="11" t="n">
         <v>0.33</v>
@@ -8361,19 +8361,19 @@
         <v>143.588</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>0.381706</v>
+        <v>0.38</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>3.791301</v>
+        <v>3.79</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>143.331326</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>0.601401</v>
+        <v>0.6</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>4.51917</v>
+        <v>4.52</v>
       </c>
       <c r="I102" s="7" t="n">
         <v>0.92</v>
@@ -8445,19 +8445,19 @@
         <v>144.307</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>0.500738</v>
+        <v>0.5</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>4.023038</v>
+        <v>4.02</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>143.98976</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>0.459379</v>
+        <v>0.46</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>4.497411</v>
+        <v>4.5</v>
       </c>
       <c r="I103" s="11" t="n">
         <v>0.39</v>
@@ -8529,19 +8529,19 @@
         <v>145.544</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>0.8572</v>
+        <v>0.86</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>4.586774</v>
+        <v>4.59</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>144.543429</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>0.384519</v>
+        <v>0.38</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>4.449385</v>
+        <v>4.45</v>
       </c>
       <c r="I104" s="7" t="n">
         <v>0.29</v>
@@ -8613,19 +8613,19 @@
         <v>145.831</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>0.197191</v>
+        <v>0.2</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>4.448503</v>
+        <v>4.45</v>
       </c>
       <c r="F105" s="10" t="n">
         <v>144.991329</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.309872</v>
+        <v>0.31</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>4.261182</v>
+        <v>4.26</v>
       </c>
       <c r="I105" s="11" t="n">
         <v>0.31</v>
@@ -8697,19 +8697,19 @@
         <v>145.527</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>-0.20846</v>
+        <v>-0.21</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>3.938948</v>
+        <v>3.94</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>145.315299</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.223441</v>
+        <v>0.22</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>4.186559</v>
+        <v>4.19</v>
       </c>
       <c r="I106" s="7" t="n">
         <v>0.16</v>
@@ -8781,19 +8781,19 @@
         <v>145.131</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>-0.272114</v>
+        <v>-0.27</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>3.365977</v>
+        <v>3.37</v>
       </c>
       <c r="F107" s="10" t="n">
         <v>145.671279</v>
       </c>
       <c r="G107" s="11" t="n">
-        <v>0.24497</v>
+        <v>0.24</v>
       </c>
       <c r="H107" s="11" t="n">
-        <v>4.03192</v>
+        <v>4.03</v>
       </c>
       <c r="I107" s="11" t="n">
         <v>0.18</v>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X108"/>
+  <dimension ref="A1:X109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8865,19 +8865,19 @@
         <v>145.169</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>0.03</v>
+        <v>0.026183</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>3.12</v>
+        <v>3.11763</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>146.000093</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>0.23</v>
+        <v>0.225723</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>3.95</v>
+        <v>3.948334</v>
       </c>
       <c r="I108" s="7" t="n">
         <v>0.19</v>
@@ -8931,6 +8931,86 @@
         </is>
       </c>
       <c r="X108" s="9" t="inlineStr">
+        <is>
+          <t>7 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H109" s="11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J109" s="11" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="K109" s="11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L109" s="11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M109" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N109" s="11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O109" s="11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P109" s="11" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="Q109" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R109" s="11" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="S109" s="12" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="T109" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U109" s="13" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V109" s="13" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W109" s="13" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/inpc/inpc_2q2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X109" s="13" t="inlineStr">
         <is>
           <t>7 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/INPC/INPC_datos.xlsx
+++ b/downloads/indicadores/INPC/INPC_datos.xlsx
@@ -8945,14 +8945,18 @@
       <c r="B109" s="5" t="n">
         <v>46235</v>
       </c>
-      <c r="C109" s="10" t="n"/>
+      <c r="C109" s="10" t="n">
+        <v>145.462</v>
+      </c>
       <c r="D109" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="E109" s="11" t="n">
         <v>3.26</v>
       </c>
-      <c r="F109" s="10" t="n"/>
+      <c r="F109" s="10" t="n">
+        <v>146.22885</v>
+      </c>
       <c r="G109" s="11" t="n">
         <v>0.16</v>
       </c>
